--- a/model/Outputs/11. Interest rate/30/Output Files/0.2/Output_12_35.xlsx
+++ b/model/Outputs/11. Interest rate/30/Output Files/0.2/Output_12_35.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2036747.632277951</v>
+        <v>2037818.755990224</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14697842.82031942</v>
+        <v>14697842.82031958</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14697842.82031942</v>
+        <v>14697842.82031958</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>657188.6984939934</v>
+        <v>657188.6984940871</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>657188.6984939934</v>
+        <v>657188.6984940871</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>31155692.28278467</v>
+        <v>31155692.28278463</v>
       </c>
     </row>
   </sheetData>
@@ -657,7 +657,7 @@
         <v>81.99931295557451</v>
       </c>
       <c r="C2" t="n">
-        <v>51.27326611082044</v>
+        <v>49.47457824299391</v>
       </c>
       <c r="D2" t="n">
         <v>10.33915573984979</v>
@@ -675,7 +675,7 @@
         <v>3.81023156784903</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1.79868786782652</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -742,19 +742,19 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>325.5201396486123</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>330.0491815260438</v>
       </c>
       <c r="I3" t="n">
-        <v>172.8521737920021</v>
+        <v>209.5726123064429</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -781,10 +781,10 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>133.6519859716245</v>
+        <v>374</v>
       </c>
       <c r="S3" t="n">
-        <v>62.48881128536601</v>
+        <v>137.6795167762956</v>
       </c>
       <c r="T3" t="n">
         <v>4.473444462796863</v>
@@ -973,16 +973,16 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>132.0068113193048</v>
       </c>
       <c r="R6" t="n">
-        <v>374</v>
+        <v>133.6519859716246</v>
       </c>
       <c r="S6" t="n">
-        <v>374</v>
+        <v>62.48881128536602</v>
       </c>
       <c r="T6" t="n">
-        <v>374</v>
+        <v>4.473444462796834</v>
       </c>
       <c r="U6" t="n">
         <v>0.1959257979225968</v>
       </c>
       <c r="V6" t="n">
-        <v>273.8055619117115</v>
+        <v>14.51066719152016</v>
       </c>
       <c r="W6" t="n">
         <v>32.37314290982852</v>
@@ -1149,7 +1149,7 @@
         <v>3.81023156784903</v>
       </c>
       <c r="I8" t="n">
-        <v>1.79868786782652</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.798687867826661</v>
       </c>
       <c r="S8" t="n">
         <v>85.50414770182039</v>
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>209.5726123064429</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1252,7 +1252,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>91.24972170815516</v>
+        <v>145.073529241423</v>
       </c>
       <c r="R9" t="n">
         <v>133.6519859716245</v>
@@ -1261,22 +1261,22 @@
         <v>62.48881128536601</v>
       </c>
       <c r="T9" t="n">
-        <v>4.473444462796863</v>
+        <v>95.40804346981558</v>
       </c>
       <c r="U9" t="n">
-        <v>374</v>
+        <v>0.1959257979225981</v>
       </c>
       <c r="V9" t="n">
         <v>14.51066719152016</v>
       </c>
       <c r="W9" t="n">
-        <v>374</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X9" t="n">
         <v>19.86273944538755</v>
       </c>
       <c r="Y9" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1368,7 +1368,7 @@
         <v>162.9993129555745</v>
       </c>
       <c r="C11" t="n">
-        <v>130.4745782429939</v>
+        <v>129.778493246499</v>
       </c>
       <c r="D11" t="n">
         <v>91.33915573984979</v>
@@ -1380,10 +1380,10 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G11" t="n">
-        <v>82.58591040609919</v>
+        <v>83.28199540259408</v>
       </c>
       <c r="H11" t="n">
-        <v>73.89995518593948</v>
+        <v>73.89995518593946</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1444,25 +1444,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>65.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C12" t="n">
-        <v>42.09991244551929</v>
+        <v>192.7286559643718</v>
       </c>
       <c r="D12" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E12" t="n">
-        <v>342.6720972219126</v>
+        <v>23.67209722191262</v>
       </c>
       <c r="F12" t="n">
         <v>20.63624233787687</v>
       </c>
       <c r="G12" t="n">
-        <v>5.950139648612248</v>
+        <v>5.950139648612264</v>
       </c>
       <c r="H12" t="n">
-        <v>5.544181526043773</v>
+        <v>5.544181526043758</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1492,16 +1492,16 @@
         <v>72.31352924142297</v>
       </c>
       <c r="R12" t="n">
-        <v>329.890729490477</v>
+        <v>179.2619859716245</v>
       </c>
       <c r="S12" t="n">
         <v>132.901311285366</v>
       </c>
       <c r="T12" t="n">
-        <v>83.17594446279683</v>
+        <v>83.17594446279685</v>
       </c>
       <c r="U12" t="n">
-        <v>81.1584257979226</v>
+        <v>81.15842579792258</v>
       </c>
       <c r="V12" t="n">
         <v>95.51066719152016</v>
@@ -1553,10 +1553,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>6.155529797123435</v>
+        <v>6.155529797123449</v>
       </c>
       <c r="M13" t="n">
-        <v>97.89093927140236</v>
+        <v>97.89093927140237</v>
       </c>
       <c r="N13" t="n">
         <v>150.9111244520127</v>
@@ -1565,16 +1565,16 @@
         <v>227.9026788331133</v>
       </c>
       <c r="P13" t="n">
-        <v>288.4057989676218</v>
+        <v>285.5554374901554</v>
       </c>
       <c r="Q13" t="n">
-        <v>348.5719049481316</v>
+        <v>351.422266425598</v>
       </c>
       <c r="R13" t="n">
-        <v>377.845046013938</v>
+        <v>377.8450460139379</v>
       </c>
       <c r="S13" t="n">
-        <v>31.84005347334724</v>
+        <v>31.84005347334727</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1620,7 +1620,7 @@
         <v>82.58591040609919</v>
       </c>
       <c r="H14" t="n">
-        <v>73.89995518593948</v>
+        <v>73.89995518593946</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1681,28 +1681,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>65.55655664632661</v>
+        <v>288.4988294066022</v>
       </c>
       <c r="C15" t="n">
         <v>42.09991244551929</v>
       </c>
       <c r="D15" t="n">
-        <v>28.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E15" t="n">
-        <v>23.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F15" t="n">
         <v>20.63624233787687</v>
       </c>
       <c r="G15" t="n">
-        <v>324.9501396486123</v>
+        <v>5.950139648612264</v>
       </c>
       <c r="H15" t="n">
-        <v>324.5441815260438</v>
+        <v>5.544181526043758</v>
       </c>
       <c r="I15" t="n">
-        <v>189.9476123064429</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1729,28 +1729,28 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>179.2619859716246</v>
+        <v>179.2619859716245</v>
       </c>
       <c r="S15" t="n">
         <v>132.901311285366</v>
       </c>
       <c r="T15" t="n">
-        <v>83.17594446279683</v>
+        <v>83.17594446279685</v>
       </c>
       <c r="U15" t="n">
-        <v>114.1530862517553</v>
+        <v>81.15842579792258</v>
       </c>
       <c r="V15" t="n">
         <v>95.51066719152016</v>
       </c>
       <c r="W15" t="n">
-        <v>113.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X15" t="n">
         <v>100.8627394453875</v>
       </c>
       <c r="Y15" t="n">
-        <v>399.3913927661343</v>
+        <v>80.39139276613435</v>
       </c>
     </row>
     <row r="16">
@@ -1790,10 +1790,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>6.155529797123435</v>
+        <v>3.305168319657098</v>
       </c>
       <c r="M16" t="n">
-        <v>97.89093927140236</v>
+        <v>97.89093927140237</v>
       </c>
       <c r="N16" t="n">
         <v>150.9111244520127</v>
@@ -1808,10 +1808,10 @@
         <v>351.422266425598</v>
       </c>
       <c r="R16" t="n">
-        <v>377.845046013938</v>
+        <v>377.8450460139379</v>
       </c>
       <c r="S16" t="n">
-        <v>28.98969199588089</v>
+        <v>31.84005347334727</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1848,13 +1848,13 @@
         <v>91.33915573984979</v>
       </c>
       <c r="E17" t="n">
-        <v>85.36328960686865</v>
+        <v>84.66720461037373</v>
       </c>
       <c r="F17" t="n">
         <v>85.88962870801186</v>
       </c>
       <c r="G17" t="n">
-        <v>82.58591040609919</v>
+        <v>83.28199540259411</v>
       </c>
       <c r="H17" t="n">
         <v>73.89995518593948</v>
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>65.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C18" t="n">
-        <v>42.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D18" t="n">
         <v>28.93768689770263</v>
@@ -1966,7 +1966,7 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>402.2042587319003</v>
+        <v>179.2619859716246</v>
       </c>
       <c r="S18" t="n">
         <v>132.901311285366</v>
@@ -1975,7 +1975,7 @@
         <v>83.17594446279683</v>
       </c>
       <c r="U18" t="n">
-        <v>400.1584257979226</v>
+        <v>81.1584257979226</v>
       </c>
       <c r="V18" t="n">
         <v>95.51066719152016</v>
@@ -1984,7 +1984,7 @@
         <v>113.3731429098285</v>
       </c>
       <c r="X18" t="n">
-        <v>419.8627394453875</v>
+        <v>323.805012205663</v>
       </c>
       <c r="Y18" t="n">
         <v>399.3913927661343</v>
@@ -2085,16 +2085,16 @@
         <v>91.33915573984979</v>
       </c>
       <c r="E20" t="n">
-        <v>84.66720461044559</v>
+        <v>85.36328960686865</v>
       </c>
       <c r="F20" t="n">
         <v>85.88962870801186</v>
       </c>
       <c r="G20" t="n">
-        <v>83.28199540259411</v>
+        <v>83.28199540259408</v>
       </c>
       <c r="H20" t="n">
-        <v>73.89995518593948</v>
+        <v>73.89995518593946</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2127,7 +2127,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>142.2280170485541</v>
+        <v>141.5319320520589</v>
       </c>
       <c r="T20" t="n">
         <v>261.2171194170061</v>
@@ -2155,25 +2155,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>65.55655664632661</v>
+        <v>288.4988294066023</v>
       </c>
       <c r="C21" t="n">
         <v>42.09991244551929</v>
       </c>
       <c r="D21" t="n">
-        <v>28.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E21" t="n">
-        <v>23.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F21" t="n">
-        <v>20.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G21" t="n">
-        <v>5.950139648612248</v>
+        <v>5.950139648612264</v>
       </c>
       <c r="H21" t="n">
-        <v>5.544181526043773</v>
+        <v>5.544181526043758</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2200,25 +2200,25 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>72.31352924142297</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>329.8907294904768</v>
+        <v>179.2619859716245</v>
       </c>
       <c r="S21" t="n">
         <v>132.901311285366</v>
       </c>
       <c r="T21" t="n">
-        <v>83.17594446279683</v>
+        <v>83.17594446279685</v>
       </c>
       <c r="U21" t="n">
-        <v>400.1584257979226</v>
+        <v>81.15842579792258</v>
       </c>
       <c r="V21" t="n">
-        <v>414.5106671915202</v>
+        <v>95.51066719152016</v>
       </c>
       <c r="W21" t="n">
-        <v>432.3731429098285</v>
+        <v>113.3731429098285</v>
       </c>
       <c r="X21" t="n">
         <v>100.8627394453875</v>
@@ -2264,10 +2264,10 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>6.155529797123435</v>
+        <v>6.155529797123449</v>
       </c>
       <c r="M22" t="n">
-        <v>97.89093927140236</v>
+        <v>97.89093927140237</v>
       </c>
       <c r="N22" t="n">
         <v>150.9111244520127</v>
@@ -2282,10 +2282,10 @@
         <v>351.422266425598</v>
       </c>
       <c r="R22" t="n">
-        <v>377.845046013938</v>
+        <v>377.8450460139379</v>
       </c>
       <c r="S22" t="n">
-        <v>28.98969199588122</v>
+        <v>28.98969199588095</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2328,10 +2328,10 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G23" t="n">
-        <v>82.58591040617111</v>
+        <v>83.28199540259411</v>
       </c>
       <c r="H23" t="n">
-        <v>73.89995518593946</v>
+        <v>73.89995518593948</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2364,7 +2364,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>142.2280170485541</v>
+        <v>141.5319320520589</v>
       </c>
       <c r="T23" t="n">
         <v>261.2171194170061</v>
@@ -2395,22 +2395,22 @@
         <v>65.55655664632661</v>
       </c>
       <c r="C24" t="n">
-        <v>42.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D24" t="n">
-        <v>28.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E24" t="n">
         <v>23.67209722191262</v>
       </c>
       <c r="F24" t="n">
-        <v>20.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G24" t="n">
-        <v>5.950139648612264</v>
+        <v>5.950139648612248</v>
       </c>
       <c r="H24" t="n">
-        <v>5.544181526043758</v>
+        <v>5.544181526043773</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2437,31 +2437,31 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>72.31352924142297</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>179.2619859716245</v>
+        <v>179.2619859716246</v>
       </c>
       <c r="S24" t="n">
         <v>132.901311285366</v>
       </c>
       <c r="T24" t="n">
-        <v>83.17594446279685</v>
+        <v>83.17594446279683</v>
       </c>
       <c r="U24" t="n">
-        <v>231.7871693167751</v>
+        <v>81.1584257979226</v>
       </c>
       <c r="V24" t="n">
         <v>95.51066719152016</v>
       </c>
       <c r="W24" t="n">
-        <v>432.3731429098285</v>
+        <v>336.3154156701041</v>
       </c>
       <c r="X24" t="n">
-        <v>419.8627394453875</v>
+        <v>100.8627394453875</v>
       </c>
       <c r="Y24" t="n">
-        <v>399.3913927661343</v>
+        <v>80.39139276613435</v>
       </c>
     </row>
     <row r="25">
@@ -2501,13 +2501,13 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>6.155529797123449</v>
+        <v>6.155529797123435</v>
       </c>
       <c r="M25" t="n">
-        <v>97.89093927140237</v>
+        <v>97.89093927140236</v>
       </c>
       <c r="N25" t="n">
-        <v>150.9111244520127</v>
+        <v>148.0607629745462</v>
       </c>
       <c r="O25" t="n">
         <v>227.9026788331133</v>
@@ -2519,10 +2519,10 @@
         <v>351.422266425598</v>
       </c>
       <c r="R25" t="n">
-        <v>377.8450460139379</v>
+        <v>377.845046013938</v>
       </c>
       <c r="S25" t="n">
-        <v>28.98969199588083</v>
+        <v>31.84005347334724</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2565,7 +2565,7 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G26" t="n">
-        <v>82.58591040617024</v>
+        <v>83.28199540259408</v>
       </c>
       <c r="H26" t="n">
         <v>73.89995518593946</v>
@@ -2610,7 +2610,7 @@
         <v>330.1032663978569</v>
       </c>
       <c r="V26" t="n">
-        <v>310.8510241668239</v>
+        <v>310.154939170351</v>
       </c>
       <c r="W26" t="n">
         <v>319.3734759809475</v>
@@ -2635,7 +2635,7 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D27" t="n">
-        <v>347.9376868977026</v>
+        <v>28.93768689770263</v>
       </c>
       <c r="E27" t="n">
         <v>23.67209722191262</v>
@@ -2644,13 +2644,13 @@
         <v>20.63624233787687</v>
       </c>
       <c r="G27" t="n">
-        <v>324.9501396486123</v>
+        <v>5.950139648612264</v>
       </c>
       <c r="H27" t="n">
         <v>5.544181526043758</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>189.9476123064429</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2680,13 +2680,13 @@
         <v>179.2619859716245</v>
       </c>
       <c r="S27" t="n">
-        <v>355.8435840456416</v>
+        <v>132.901311285366</v>
       </c>
       <c r="T27" t="n">
-        <v>83.17594446279685</v>
+        <v>116.1706049166298</v>
       </c>
       <c r="U27" t="n">
-        <v>81.15842579792258</v>
+        <v>400.1584257979226</v>
       </c>
       <c r="V27" t="n">
         <v>95.51066719152016</v>
@@ -2695,7 +2695,7 @@
         <v>113.3731429098285</v>
       </c>
       <c r="X27" t="n">
-        <v>100.8627394453875</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y27" t="n">
         <v>80.39139276613435</v>
@@ -2802,10 +2802,10 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G29" t="n">
-        <v>82.58591040616571</v>
+        <v>83.28199540259408</v>
       </c>
       <c r="H29" t="n">
-        <v>73.89995518593948</v>
+        <v>73.89995518593946</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2844,7 +2844,7 @@
         <v>261.2171194170061</v>
       </c>
       <c r="U29" t="n">
-        <v>330.1032663978569</v>
+        <v>329.4071814013618</v>
       </c>
       <c r="V29" t="n">
         <v>310.8510241668239</v>
@@ -2866,25 +2866,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>288.4988294066021</v>
+        <v>65.55655664632661</v>
       </c>
       <c r="C30" t="n">
-        <v>361.0999124455193</v>
+        <v>42.09991244551929</v>
       </c>
       <c r="D30" t="n">
-        <v>347.9376868977026</v>
+        <v>28.93768689770263</v>
       </c>
       <c r="E30" t="n">
-        <v>342.6720972219126</v>
+        <v>23.67209722191262</v>
       </c>
       <c r="F30" t="n">
         <v>20.63624233787687</v>
       </c>
       <c r="G30" t="n">
-        <v>5.950139648612248</v>
+        <v>5.950139648612264</v>
       </c>
       <c r="H30" t="n">
-        <v>5.544181526043773</v>
+        <v>5.544181526043758</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2914,25 +2914,25 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>179.2619859716246</v>
+        <v>179.2619859716245</v>
       </c>
       <c r="S30" t="n">
         <v>132.901311285366</v>
       </c>
       <c r="T30" t="n">
-        <v>83.17594446279683</v>
+        <v>83.17594446279685</v>
       </c>
       <c r="U30" t="n">
-        <v>81.1584257979226</v>
+        <v>304.1006985581982</v>
       </c>
       <c r="V30" t="n">
-        <v>95.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W30" t="n">
-        <v>113.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X30" t="n">
-        <v>100.8627394453875</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y30" t="n">
         <v>80.39139276613435</v>
@@ -2975,10 +2975,10 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>3.305168319657323</v>
+        <v>6.155529797123449</v>
       </c>
       <c r="M31" t="n">
-        <v>97.89093927140236</v>
+        <v>97.89093927140237</v>
       </c>
       <c r="N31" t="n">
         <v>150.9111244520127</v>
@@ -2993,10 +2993,10 @@
         <v>351.422266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>377.845046013938</v>
+        <v>377.8450460139379</v>
       </c>
       <c r="S31" t="n">
-        <v>31.84005347334724</v>
+        <v>28.98969199588095</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -3042,7 +3042,7 @@
         <v>83.28199540259411</v>
       </c>
       <c r="H32" t="n">
-        <v>73.89995518593948</v>
+        <v>73.20387018951705</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -3078,7 +3078,7 @@
         <v>142.2280170485541</v>
       </c>
       <c r="T32" t="n">
-        <v>260.5210344205822</v>
+        <v>261.2171194170061</v>
       </c>
       <c r="U32" t="n">
         <v>330.1032663978569</v>
@@ -3103,10 +3103,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>65.55655664632661</v>
+        <v>216.1853001651792</v>
       </c>
       <c r="C33" t="n">
-        <v>265.042185205795</v>
+        <v>42.09991244551929</v>
       </c>
       <c r="D33" t="n">
         <v>347.9376868977026</v>
@@ -3148,7 +3148,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>72.31352924142297</v>
       </c>
       <c r="R33" t="n">
         <v>179.2619859716246</v>
@@ -3212,7 +3212,7 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>6.155529797123435</v>
+        <v>3.305168319656873</v>
       </c>
       <c r="M34" t="n">
         <v>97.89093927140236</v>
@@ -3227,7 +3227,7 @@
         <v>288.4057989676218</v>
       </c>
       <c r="Q34" t="n">
-        <v>348.5719049481319</v>
+        <v>351.422266425598</v>
       </c>
       <c r="R34" t="n">
         <v>377.845046013938</v>
@@ -3312,10 +3312,10 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>60.92708723806961</v>
+        <v>64.22801704855405</v>
       </c>
       <c r="T35" t="n">
-        <v>183.2171194170061</v>
+        <v>179.9161896064505</v>
       </c>
       <c r="U35" t="n">
         <v>252.1032663978569</v>
@@ -3340,13 +3340,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>374.0000000000492</v>
+        <v>374.0000000000273</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D36" t="n">
-        <v>347.9376868977026</v>
+        <v>117.1943449153656</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -3385,7 +3385,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>72.31352924142297</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>101.2619859716246</v>
@@ -3400,16 +3400,16 @@
         <v>3.158425797922597</v>
       </c>
       <c r="V36" t="n">
-        <v>17.51066719152016</v>
+        <v>374.0000000000273</v>
       </c>
       <c r="W36" t="n">
         <v>35.37314290982852</v>
       </c>
       <c r="X36" t="n">
-        <v>65.78650624178829</v>
+        <v>22.86273944538755</v>
       </c>
       <c r="Y36" t="n">
-        <v>374.0000000000492</v>
+        <v>2.391392766134345</v>
       </c>
     </row>
     <row r="37">
@@ -3510,10 +3510,10 @@
         <v>7.363289606868648</v>
       </c>
       <c r="F38" t="n">
-        <v>7.889628708011855</v>
+        <v>4.588698897456261</v>
       </c>
       <c r="G38" t="n">
-        <v>5.2819954025941</v>
+        <v>5.281995402594077</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -3549,13 +3549,13 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>64.22801704855405</v>
+        <v>64.22801704855408</v>
       </c>
       <c r="T38" t="n">
         <v>183.2171194170061</v>
       </c>
       <c r="U38" t="n">
-        <v>248.8023365873724</v>
+        <v>252.1032663978569</v>
       </c>
       <c r="V38" t="n">
         <v>232.8510241668239</v>
@@ -3583,13 +3583,13 @@
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -3622,31 +3622,31 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>72.31352924142297</v>
       </c>
       <c r="R39" t="n">
-        <v>101.2619859716246</v>
+        <v>101.2619859716245</v>
       </c>
       <c r="S39" t="n">
-        <v>54.90131128536602</v>
+        <v>54.90131128536603</v>
       </c>
       <c r="T39" t="n">
-        <v>5.175944462796835</v>
+        <v>5.175944462796849</v>
       </c>
       <c r="U39" t="n">
-        <v>3.158425797922597</v>
+        <v>3.158425797922575</v>
       </c>
       <c r="V39" t="n">
-        <v>17.51066719152016</v>
+        <v>374.0000000000601</v>
       </c>
       <c r="W39" t="n">
-        <v>35.37314290982852</v>
+        <v>374.0000000000601</v>
       </c>
       <c r="X39" t="n">
-        <v>201.4003031573857</v>
+        <v>374.0000000000601</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.391392766134345</v>
+        <v>92.6080032406869</v>
       </c>
     </row>
     <row r="40">
@@ -3689,10 +3689,10 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>19.89093927140236</v>
+        <v>19.89093927140237</v>
       </c>
       <c r="N40" t="n">
-        <v>72.91112445201273</v>
+        <v>72.9111244520127</v>
       </c>
       <c r="O40" t="n">
         <v>149.9026788331133</v>
@@ -3704,7 +3704,7 @@
         <v>273.422266425598</v>
       </c>
       <c r="R40" t="n">
-        <v>299.845046013938</v>
+        <v>299.8450460139379</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -3741,16 +3741,16 @@
         <v>156.4745782429939</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>117.3391557398498</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>24.78581282175835</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>111.8896287080119</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>109.2819954025941</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -3786,25 +3786,25 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>124.4389751930635</v>
+        <v>168.2280170485541</v>
       </c>
       <c r="T41" t="n">
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>356.1032663978569</v>
       </c>
       <c r="V41" t="n">
-        <v>336.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>345.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>299.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>218.3174326828064</v>
       </c>
     </row>
     <row r="42">
@@ -3829,13 +3829,13 @@
         <v>46.63624233787687</v>
       </c>
       <c r="G42" t="n">
-        <v>31.95013964861225</v>
+        <v>31.95013964861226</v>
       </c>
       <c r="H42" t="n">
-        <v>31.54418152604377</v>
+        <v>31.54418152604376</v>
       </c>
       <c r="I42" t="n">
-        <v>2.38677344549622</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3862,7 +3862,7 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>205.2619859716246</v>
+        <v>207.6487594170497</v>
       </c>
       <c r="S42" t="n">
         <v>158.901311285366</v>
@@ -3923,7 +3923,7 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>32.15552979712344</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -3935,16 +3935,16 @@
         <v>253.9026788331133</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>314.4057989676218</v>
       </c>
       <c r="Q43" t="n">
-        <v>374.0000000005258</v>
+        <v>374.0000000000837</v>
       </c>
       <c r="R43" t="n">
-        <v>226.9920892005681</v>
+        <v>2.581873503859331</v>
       </c>
       <c r="S43" t="n">
-        <v>57.84005347334724</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3972,25 +3972,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>188.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>156.4745782429939</v>
+        <v>113.8095999937039</v>
       </c>
       <c r="D44" t="n">
-        <v>117.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>111.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>111.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>79.52595155467198</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -4023,25 +4023,25 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>168.2280170485541</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>356.1032663978569</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>336.8510241668239</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>345.3734759809475</v>
       </c>
       <c r="X44" t="n">
         <v>299.2818334606677</v>
       </c>
       <c r="Y44" t="n">
-        <v>218.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -4066,13 +4066,13 @@
         <v>46.63624233787687</v>
       </c>
       <c r="G45" t="n">
-        <v>31.95013964861226</v>
+        <v>31.95013964861225</v>
       </c>
       <c r="H45" t="n">
-        <v>31.54418152604376</v>
+        <v>31.54418152604377</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>2.386773445425186</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4096,10 +4096,10 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.386773445424244</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>205.2619859716245</v>
+        <v>205.2619859716246</v>
       </c>
       <c r="S45" t="n">
         <v>158.901311285366</v>
@@ -4163,7 +4163,7 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>2.581873503761117</v>
       </c>
       <c r="N46" t="n">
         <v>176.9111244520127</v>
@@ -4175,10 +4175,10 @@
         <v>314.4057989676218</v>
       </c>
       <c r="Q46" t="n">
-        <v>374.0000000001892</v>
+        <v>374.000000000182</v>
       </c>
       <c r="R46" t="n">
-        <v>2.581873503753833</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -4300,46 +4300,46 @@
         <v>108.731003807232</v>
       </c>
       <c r="C2" t="n">
-        <v>56.9398259175144</v>
+        <v>58.7566823496624</v>
       </c>
       <c r="D2" t="n">
-        <v>46.49623426110047</v>
+        <v>48.31309069324847</v>
       </c>
       <c r="E2" t="n">
-        <v>42.08887102183921</v>
+        <v>43.90572745398721</v>
       </c>
       <c r="F2" t="n">
-        <v>37.14985212485754</v>
+        <v>38.96670855700554</v>
       </c>
       <c r="G2" t="n">
-        <v>33.76871875540306</v>
+        <v>35.58557518755106</v>
       </c>
       <c r="H2" t="n">
-        <v>29.92</v>
+        <v>31.736856432148</v>
       </c>
       <c r="I2" t="n">
         <v>29.92</v>
       </c>
       <c r="J2" t="n">
-        <v>400.18</v>
+        <v>29.92</v>
       </c>
       <c r="K2" t="n">
-        <v>451.8183303517587</v>
+        <v>81.5583303517588</v>
       </c>
       <c r="L2" t="n">
-        <v>515.8802453266331</v>
+        <v>145.6202453266332</v>
       </c>
       <c r="M2" t="n">
-        <v>886.1402453266331</v>
+        <v>327.128108133742</v>
       </c>
       <c r="N2" t="n">
-        <v>1256.400245326633</v>
+        <v>697.388108133742</v>
       </c>
       <c r="O2" t="n">
-        <v>1256.400245326633</v>
+        <v>1067.648108133742</v>
       </c>
       <c r="P2" t="n">
-        <v>1314.492137192891</v>
+        <v>1125.74</v>
       </c>
       <c r="Q2" t="n">
         <v>1496</v>
@@ -4376,25 +4376,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1225.740689833893</v>
+        <v>907.0147105214633</v>
       </c>
       <c r="C3" t="n">
-        <v>1225.740689833893</v>
+        <v>907.0147105214633</v>
       </c>
       <c r="D3" t="n">
-        <v>1225.740689833893</v>
+        <v>907.0147105214633</v>
       </c>
       <c r="E3" t="n">
-        <v>879.6072582966071</v>
+        <v>907.0147105214633</v>
       </c>
       <c r="F3" t="n">
-        <v>536.5403468442062</v>
+        <v>907.0147105214633</v>
       </c>
       <c r="G3" t="n">
-        <v>207.7321249769211</v>
+        <v>578.2064886541781</v>
       </c>
       <c r="H3" t="n">
-        <v>207.7321249769211</v>
+        <v>244.8234770117097</v>
       </c>
       <c r="I3" t="n">
         <v>33.13396963146437</v>
@@ -4424,28 +4424,28 @@
         <v>1496</v>
       </c>
       <c r="R3" t="n">
-        <v>1360.997993968056</v>
+        <v>1118.222222222222</v>
       </c>
       <c r="S3" t="n">
-        <v>1297.877982568697</v>
+        <v>979.152003256267</v>
       </c>
       <c r="T3" t="n">
-        <v>1293.359351798195</v>
+        <v>974.6333724857651</v>
       </c>
       <c r="U3" t="n">
-        <v>1293.161446951808</v>
+        <v>974.4354676393787</v>
       </c>
       <c r="V3" t="n">
-        <v>1278.504207364414</v>
+        <v>959.7782280519846</v>
       </c>
       <c r="W3" t="n">
-        <v>1245.804063011052</v>
+        <v>927.0780836986224</v>
       </c>
       <c r="X3" t="n">
-        <v>1225.740689833893</v>
+        <v>907.0147105214633</v>
       </c>
       <c r="Y3" t="n">
-        <v>1225.740689833893</v>
+        <v>907.0147105214633</v>
       </c>
     </row>
     <row r="4">
@@ -4455,34 +4455,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>973.4180956823087</v>
+        <v>650.678554466821</v>
       </c>
       <c r="C4" t="n">
-        <v>973.4180956823087</v>
+        <v>776.6805602852568</v>
       </c>
       <c r="D4" t="n">
-        <v>973.4180956823087</v>
+        <v>889.9997044102569</v>
       </c>
       <c r="E4" t="n">
-        <v>1091.246999893722</v>
+        <v>1007.82860862167</v>
       </c>
       <c r="F4" t="n">
-        <v>1215.607972485657</v>
+        <v>1132.189581213605</v>
       </c>
       <c r="G4" t="n">
-        <v>1215.607972485657</v>
+        <v>1132.189581213605</v>
       </c>
       <c r="H4" t="n">
-        <v>1386.743548464727</v>
+        <v>1251.462556240126</v>
       </c>
       <c r="I4" t="n">
-        <v>1386.743548464727</v>
+        <v>1251.462556240126</v>
       </c>
       <c r="J4" t="n">
-        <v>1386.743548464727</v>
+        <v>1251.462556240126</v>
       </c>
       <c r="K4" t="n">
-        <v>1386.743548464727</v>
+        <v>1382.983127881912</v>
       </c>
       <c r="L4" t="n">
         <v>1386.743548464727</v>
@@ -4506,25 +4506,25 @@
         <v>29.92</v>
       </c>
       <c r="S4" t="n">
-        <v>70.34367574991084</v>
+        <v>29.92</v>
       </c>
       <c r="T4" t="n">
-        <v>70.34367574991084</v>
+        <v>29.92</v>
       </c>
       <c r="U4" t="n">
-        <v>316.9048008472139</v>
+        <v>276.481125097303</v>
       </c>
       <c r="V4" t="n">
-        <v>515.7261937331598</v>
+        <v>276.481125097303</v>
       </c>
       <c r="W4" t="n">
-        <v>687.6171119928372</v>
+        <v>276.481125097303</v>
       </c>
       <c r="X4" t="n">
-        <v>838.6479030170307</v>
+        <v>427.5119161214966</v>
       </c>
       <c r="Y4" t="n">
-        <v>950.057203696063</v>
+        <v>538.9212168005289</v>
       </c>
     </row>
     <row r="5">
@@ -4561,13 +4561,13 @@
         <v>29.92</v>
       </c>
       <c r="K5" t="n">
-        <v>263.0661931588676</v>
+        <v>400.18</v>
       </c>
       <c r="L5" t="n">
-        <v>327.128108133742</v>
+        <v>464.2419149748744</v>
       </c>
       <c r="M5" t="n">
-        <v>697.388108133742</v>
+        <v>834.5019149748744</v>
       </c>
       <c r="N5" t="n">
         <v>1067.648108133742</v>
@@ -4613,16 +4613,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>29.92</v>
+        <v>1089.186506748585</v>
       </c>
       <c r="C6" t="n">
-        <v>29.92</v>
+        <v>724.4391204399794</v>
       </c>
       <c r="D6" t="n">
-        <v>29.92</v>
+        <v>372.9869114524009</v>
       </c>
       <c r="E6" t="n">
-        <v>29.92</v>
+        <v>372.9869114524009</v>
       </c>
       <c r="F6" t="n">
         <v>29.92</v>
@@ -4658,31 +4658,31 @@
         <v>1492.786030368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1492.786030368536</v>
+        <v>1359.445816914692</v>
       </c>
       <c r="R6" t="n">
-        <v>1115.008252590758</v>
+        <v>1224.443810882748</v>
       </c>
       <c r="S6" t="n">
-        <v>737.23047481298</v>
+        <v>1161.323799483389</v>
       </c>
       <c r="T6" t="n">
-        <v>359.4526970352022</v>
+        <v>1156.805168712887</v>
       </c>
       <c r="U6" t="n">
-        <v>359.2547921888157</v>
+        <v>1156.6072638665</v>
       </c>
       <c r="V6" t="n">
-        <v>82.68351753052127</v>
+        <v>1141.950024279106</v>
       </c>
       <c r="W6" t="n">
-        <v>49.98337317715914</v>
+        <v>1109.249879925744</v>
       </c>
       <c r="X6" t="n">
-        <v>29.92</v>
+        <v>1089.186506748585</v>
       </c>
       <c r="Y6" t="n">
-        <v>29.92</v>
+        <v>1089.186506748585</v>
       </c>
     </row>
     <row r="7">
@@ -4692,28 +4692,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>292.7081286904856</v>
+        <v>496.5679514324188</v>
       </c>
       <c r="C7" t="n">
-        <v>292.7081286904856</v>
+        <v>622.5699572508546</v>
       </c>
       <c r="D7" t="n">
-        <v>292.7081286904856</v>
+        <v>735.8891013758547</v>
       </c>
       <c r="E7" t="n">
-        <v>410.5370329018987</v>
+        <v>853.7180055872677</v>
       </c>
       <c r="F7" t="n">
-        <v>534.8980054938341</v>
+        <v>853.7180055872677</v>
       </c>
       <c r="G7" t="n">
-        <v>688.4866664626866</v>
+        <v>853.7180055872677</v>
       </c>
       <c r="H7" t="n">
-        <v>859.6222424417563</v>
+        <v>1024.853581566337</v>
       </c>
       <c r="I7" t="n">
-        <v>1086.231217115544</v>
+        <v>1251.462556240125</v>
       </c>
       <c r="J7" t="n">
         <v>1251.462556240125</v>
@@ -4743,25 +4743,25 @@
         <v>29.92</v>
       </c>
       <c r="S7" t="n">
-        <v>29.92</v>
+        <v>70.34367574991083</v>
       </c>
       <c r="T7" t="n">
-        <v>29.92</v>
+        <v>259.1973975316665</v>
       </c>
       <c r="U7" t="n">
-        <v>29.92</v>
+        <v>384.8106137661267</v>
       </c>
       <c r="V7" t="n">
-        <v>29.92</v>
+        <v>384.8106137661267</v>
       </c>
       <c r="W7" t="n">
-        <v>29.92</v>
+        <v>384.8106137661267</v>
       </c>
       <c r="X7" t="n">
-        <v>180.9507910241935</v>
+        <v>384.8106137661267</v>
       </c>
       <c r="Y7" t="n">
-        <v>180.9507910241935</v>
+        <v>384.8106137661267</v>
       </c>
     </row>
     <row r="8">
@@ -4771,76 +4771,76 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>108.731003807232</v>
+        <v>106.914147375084</v>
       </c>
       <c r="C8" t="n">
-        <v>58.7566823496624</v>
+        <v>56.9398259175144</v>
       </c>
       <c r="D8" t="n">
-        <v>48.31309069324847</v>
+        <v>46.49623426110047</v>
       </c>
       <c r="E8" t="n">
-        <v>43.90572745398721</v>
+        <v>42.08887102183921</v>
       </c>
       <c r="F8" t="n">
-        <v>38.96670855700554</v>
+        <v>37.14985212485754</v>
       </c>
       <c r="G8" t="n">
-        <v>35.58557518755106</v>
+        <v>33.76871875540306</v>
       </c>
       <c r="H8" t="n">
-        <v>31.736856432148</v>
+        <v>29.92</v>
       </c>
       <c r="I8" t="n">
         <v>29.92</v>
       </c>
       <c r="J8" t="n">
+        <v>29.92</v>
+      </c>
+      <c r="K8" t="n">
         <v>400.18</v>
       </c>
-      <c r="K8" t="n">
-        <v>770.4399999999999</v>
-      </c>
       <c r="L8" t="n">
-        <v>1140.7</v>
+        <v>464.2419149748744</v>
       </c>
       <c r="M8" t="n">
-        <v>1437.908108133742</v>
+        <v>834.5019149748744</v>
       </c>
       <c r="N8" t="n">
-        <v>1437.908108133742</v>
+        <v>1204.761914974874</v>
       </c>
       <c r="O8" t="n">
-        <v>1437.908108133742</v>
+        <v>1204.761914974874</v>
       </c>
       <c r="P8" t="n">
-        <v>1496</v>
+        <v>1262.853806841132</v>
       </c>
       <c r="Q8" t="n">
         <v>1496</v>
       </c>
       <c r="R8" t="n">
-        <v>1496</v>
+        <v>1494.183143567852</v>
       </c>
       <c r="S8" t="n">
-        <v>1409.632174038565</v>
+        <v>1407.815317606417</v>
       </c>
       <c r="T8" t="n">
-        <v>1222.884106610596</v>
+        <v>1221.067250178448</v>
       </c>
       <c r="U8" t="n">
-        <v>971.1785586019998</v>
+        <v>969.3617021698518</v>
       </c>
       <c r="V8" t="n">
-        <v>739.0058069183393</v>
+        <v>737.1889504861913</v>
       </c>
       <c r="W8" t="n">
-        <v>498.2245180486953</v>
+        <v>496.4076616165473</v>
       </c>
       <c r="X8" t="n">
-        <v>304.0004438460006</v>
+        <v>302.1835874138526</v>
       </c>
       <c r="Y8" t="n">
-        <v>191.5585926512467</v>
+        <v>189.7417362190987</v>
       </c>
     </row>
     <row r="9">
@@ -4850,25 +4850,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29.92</v>
+        <v>606.3568936888507</v>
       </c>
       <c r="C9" t="n">
-        <v>29.92</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="D9" t="n">
-        <v>29.92</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="E9" t="n">
-        <v>29.92</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="F9" t="n">
-        <v>29.92</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="G9" t="n">
-        <v>29.92</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="H9" t="n">
-        <v>29.92</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="I9" t="n">
         <v>29.92</v>
@@ -4895,31 +4895,31 @@
         <v>1492.786030368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1400.614594299692</v>
+        <v>1346.247111942856</v>
       </c>
       <c r="R9" t="n">
-        <v>1265.612588267748</v>
+        <v>1211.245105910912</v>
       </c>
       <c r="S9" t="n">
-        <v>1202.492576868389</v>
+        <v>1148.125094511552</v>
       </c>
       <c r="T9" t="n">
-        <v>1197.973946097887</v>
+        <v>1051.753333430931</v>
       </c>
       <c r="U9" t="n">
-        <v>820.1961683201089</v>
+        <v>1051.555428584544</v>
       </c>
       <c r="V9" t="n">
-        <v>805.5389287327148</v>
+        <v>1036.89818899715</v>
       </c>
       <c r="W9" t="n">
-        <v>427.761150954937</v>
+        <v>1004.198044643788</v>
       </c>
       <c r="X9" t="n">
-        <v>407.6977777777778</v>
+        <v>984.1346714666286</v>
       </c>
       <c r="Y9" t="n">
-        <v>29.92</v>
+        <v>984.1346714666286</v>
       </c>
     </row>
     <row r="10">
@@ -4929,19 +4929,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>909.6335279461522</v>
+        <v>839.5322762485766</v>
       </c>
       <c r="C10" t="n">
-        <v>1035.635533764588</v>
+        <v>965.5342820670124</v>
       </c>
       <c r="D10" t="n">
-        <v>1148.954677889588</v>
+        <v>1078.853426192012</v>
       </c>
       <c r="E10" t="n">
-        <v>1266.783582101001</v>
+        <v>1196.682330403425</v>
       </c>
       <c r="F10" t="n">
-        <v>1386.743548464727</v>
+        <v>1321.043302995361</v>
       </c>
       <c r="G10" t="n">
         <v>1386.743548464727</v>
@@ -4983,22 +4983,22 @@
         <v>29.92</v>
       </c>
       <c r="T10" t="n">
-        <v>29.92</v>
+        <v>218.7737217817557</v>
       </c>
       <c r="U10" t="n">
-        <v>276.481125097303</v>
+        <v>465.3348468790587</v>
       </c>
       <c r="V10" t="n">
-        <v>475.302517983249</v>
+        <v>465.3348468790587</v>
       </c>
       <c r="W10" t="n">
-        <v>647.1934362429264</v>
+        <v>465.3348468790587</v>
       </c>
       <c r="X10" t="n">
-        <v>798.2242272671199</v>
+        <v>616.3656379032523</v>
       </c>
       <c r="Y10" t="n">
-        <v>909.6335279461522</v>
+        <v>727.7749385822846</v>
       </c>
     </row>
     <row r="11">
@@ -5011,16 +5011,16 @@
         <v>607.5035534240029</v>
       </c>
       <c r="C11" t="n">
-        <v>475.7110501482515</v>
+        <v>476.4141663063272</v>
       </c>
       <c r="D11" t="n">
-        <v>383.4492766736557</v>
+        <v>384.1523928317314</v>
       </c>
       <c r="E11" t="n">
-        <v>297.2237316162127</v>
+        <v>297.9268477742883</v>
       </c>
       <c r="F11" t="n">
-        <v>210.4665309010492</v>
+        <v>211.1696470591248</v>
       </c>
       <c r="G11" t="n">
         <v>127.0464193797368</v>
@@ -5038,10 +5038,10 @@
         <v>753.4744118316256</v>
       </c>
       <c r="L11" t="n">
-        <v>983.9716941431833</v>
+        <v>1401.924411831626</v>
       </c>
       <c r="M11" t="n">
-        <v>1585.241587554807</v>
+        <v>2050.374411831625</v>
       </c>
       <c r="N11" t="n">
         <v>2233.691587554807</v>
@@ -5087,13 +5087,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>824.9659192703713</v>
+        <v>654.8939430267878</v>
       </c>
       <c r="C12" t="n">
-        <v>782.4407551839881</v>
+        <v>460.2185329617658</v>
       </c>
       <c r="D12" t="n">
-        <v>430.9885461964096</v>
+        <v>108.7663239741874</v>
       </c>
       <c r="E12" t="n">
         <v>84.85511465912413</v>
@@ -5102,7 +5102,7 @@
         <v>64.01042542894548</v>
       </c>
       <c r="G12" t="n">
-        <v>58.00018335964018</v>
+        <v>58.00018335964016</v>
       </c>
       <c r="H12" t="n">
         <v>52.4</v>
@@ -5135,28 +5135,28 @@
         <v>2240.946636437805</v>
       </c>
       <c r="R12" t="n">
-        <v>1907.723677356516</v>
+        <v>2059.873923335154</v>
       </c>
       <c r="S12" t="n">
-        <v>1773.479928583419</v>
+        <v>1925.630174562057</v>
       </c>
       <c r="T12" t="n">
-        <v>1689.463823065442</v>
+        <v>1841.614069044081</v>
       </c>
       <c r="U12" t="n">
-        <v>1607.485615188752</v>
+        <v>1759.635861167391</v>
       </c>
       <c r="V12" t="n">
-        <v>1511.010193783176</v>
+        <v>1663.160439761815</v>
       </c>
       <c r="W12" t="n">
-        <v>1074.26964538941</v>
+        <v>1226.419891368049</v>
       </c>
       <c r="X12" t="n">
-        <v>972.3880903940692</v>
+        <v>1124.538336372708</v>
       </c>
       <c r="Y12" t="n">
-        <v>891.1846633575699</v>
+        <v>1043.334909336209</v>
       </c>
     </row>
     <row r="13">
@@ -5166,31 +5166,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>673.4417775581344</v>
+        <v>673.4417775581345</v>
       </c>
       <c r="C13" t="n">
-        <v>719.2537833765701</v>
+        <v>719.2537833765703</v>
       </c>
       <c r="D13" t="n">
-        <v>752.3829275015702</v>
+        <v>752.3829275015703</v>
       </c>
       <c r="E13" t="n">
-        <v>790.0218317129832</v>
+        <v>790.0218317129833</v>
       </c>
       <c r="F13" t="n">
-        <v>834.1928043049187</v>
+        <v>834.1928043049188</v>
       </c>
       <c r="G13" t="n">
-        <v>908.0645554377056</v>
+        <v>908.0645554377057</v>
       </c>
       <c r="H13" t="n">
         <v>1003.21633305612</v>
       </c>
       <c r="I13" t="n">
-        <v>1163.862419205317</v>
+        <v>1163.862419205318</v>
       </c>
       <c r="J13" t="n">
-        <v>1491.077756743014</v>
+        <v>1491.077756743015</v>
       </c>
       <c r="K13" t="n">
         <v>1597.372803794637</v>
@@ -5199,7 +5199,7 @@
         <v>1591.155096928856</v>
       </c>
       <c r="M13" t="n">
-        <v>1492.275360291075</v>
+        <v>1492.275360291076</v>
       </c>
       <c r="N13" t="n">
         <v>1339.839881046618</v>
@@ -5208,13 +5208,13 @@
         <v>1109.635154952564</v>
       </c>
       <c r="P13" t="n">
-        <v>818.3161660963807</v>
+        <v>821.1953191039224</v>
       </c>
       <c r="Q13" t="n">
-        <v>466.2233328154397</v>
+        <v>466.2233328154396</v>
       </c>
       <c r="R13" t="n">
-        <v>84.56167017509823</v>
+        <v>84.56167017509824</v>
       </c>
       <c r="S13" t="n">
         <v>52.4</v>
@@ -5223,19 +5223,19 @@
         <v>163.0851070276573</v>
       </c>
       <c r="U13" t="n">
-        <v>329.4820370429931</v>
+        <v>329.4820370429932</v>
       </c>
       <c r="V13" t="n">
         <v>448.1134299289391</v>
       </c>
       <c r="W13" t="n">
-        <v>539.8143481886165</v>
+        <v>539.8143481886166</v>
       </c>
       <c r="X13" t="n">
-        <v>610.65513921281</v>
+        <v>610.6551392128101</v>
       </c>
       <c r="Y13" t="n">
-        <v>641.8744398918423</v>
+        <v>641.8744398918424</v>
       </c>
     </row>
     <row r="14">
@@ -5269,25 +5269,25 @@
         <v>52.4</v>
       </c>
       <c r="J14" t="n">
-        <v>567.6776741934345</v>
+        <v>141.6759849731395</v>
       </c>
       <c r="K14" t="n">
-        <v>1216.127674193434</v>
+        <v>790.1259849731395</v>
       </c>
       <c r="L14" t="n">
-        <v>1446.624956504992</v>
+        <v>1438.575984973139</v>
       </c>
       <c r="M14" t="n">
-        <v>1637.361628029778</v>
+        <v>2087.025984973139</v>
       </c>
       <c r="N14" t="n">
-        <v>1637.361628029778</v>
+        <v>2087.025984973139</v>
       </c>
       <c r="O14" t="n">
-        <v>1813.91480011625</v>
+        <v>2263.579157059612</v>
       </c>
       <c r="P14" t="n">
-        <v>2023.670040474971</v>
+        <v>2473.334397418333</v>
       </c>
       <c r="Q14" t="n">
         <v>2620</v>
@@ -5324,25 +5324,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1016.832194327384</v>
+        <v>824.9659192703713</v>
       </c>
       <c r="C15" t="n">
-        <v>974.3070302410011</v>
+        <v>782.4407551839881</v>
       </c>
       <c r="D15" t="n">
-        <v>945.0770434756449</v>
+        <v>430.9885461964096</v>
       </c>
       <c r="E15" t="n">
-        <v>921.1658341605817</v>
+        <v>84.85511465912413</v>
       </c>
       <c r="F15" t="n">
-        <v>900.321144930403</v>
+        <v>64.01042542894548</v>
       </c>
       <c r="G15" t="n">
-        <v>572.0886806388754</v>
+        <v>58.00018335964016</v>
       </c>
       <c r="H15" t="n">
-        <v>244.266275057013</v>
+        <v>52.4</v>
       </c>
       <c r="I15" t="n">
         <v>52.4</v>
@@ -5381,19 +5381,19 @@
         <v>1914.658037974811</v>
       </c>
       <c r="U15" t="n">
-        <v>1799.351890245765</v>
+        <v>1832.679830098122</v>
       </c>
       <c r="V15" t="n">
-        <v>1702.87646884019</v>
+        <v>1736.204408692546</v>
       </c>
       <c r="W15" t="n">
-        <v>1588.358142668646</v>
+        <v>1299.46386029878</v>
       </c>
       <c r="X15" t="n">
-        <v>1486.476587673304</v>
+        <v>1197.582305303438</v>
       </c>
       <c r="Y15" t="n">
-        <v>1083.050938414583</v>
+        <v>1116.378878266939</v>
       </c>
     </row>
     <row r="16">
@@ -5403,55 +5403,55 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>673.4417775581344</v>
+        <v>673.4417775581345</v>
       </c>
       <c r="C16" t="n">
-        <v>719.2537833765701</v>
+        <v>719.2537833765703</v>
       </c>
       <c r="D16" t="n">
-        <v>752.3829275015702</v>
+        <v>752.3829275015703</v>
       </c>
       <c r="E16" t="n">
-        <v>790.0218317129832</v>
+        <v>790.0218317129833</v>
       </c>
       <c r="F16" t="n">
-        <v>834.1928043049187</v>
+        <v>834.1928043049188</v>
       </c>
       <c r="G16" t="n">
-        <v>908.0645554377056</v>
+        <v>908.0645554377057</v>
       </c>
       <c r="H16" t="n">
         <v>1003.21633305612</v>
       </c>
       <c r="I16" t="n">
-        <v>1163.862419205317</v>
+        <v>1163.862419205318</v>
       </c>
       <c r="J16" t="n">
-        <v>1491.077756743014</v>
+        <v>1491.077756743015</v>
       </c>
       <c r="K16" t="n">
         <v>1597.372803794637</v>
       </c>
       <c r="L16" t="n">
-        <v>1591.155096928856</v>
+        <v>1594.034249936398</v>
       </c>
       <c r="M16" t="n">
-        <v>1492.275360291075</v>
+        <v>1495.154513298618</v>
       </c>
       <c r="N16" t="n">
-        <v>1339.839881046618</v>
+        <v>1342.71903405416</v>
       </c>
       <c r="O16" t="n">
-        <v>1109.635154952564</v>
+        <v>1112.514307960106</v>
       </c>
       <c r="P16" t="n">
-        <v>818.3161660963807</v>
+        <v>821.1953191039224</v>
       </c>
       <c r="Q16" t="n">
-        <v>463.3441798078979</v>
+        <v>466.2233328154396</v>
       </c>
       <c r="R16" t="n">
-        <v>81.68251716755645</v>
+        <v>84.56167017509824</v>
       </c>
       <c r="S16" t="n">
         <v>52.4</v>
@@ -5460,19 +5460,19 @@
         <v>163.0851070276573</v>
       </c>
       <c r="U16" t="n">
-        <v>329.4820370429931</v>
+        <v>329.4820370429932</v>
       </c>
       <c r="V16" t="n">
         <v>448.1134299289391</v>
       </c>
       <c r="W16" t="n">
-        <v>539.8143481886165</v>
+        <v>539.8143481886166</v>
       </c>
       <c r="X16" t="n">
-        <v>610.65513921281</v>
+        <v>610.6551392128101</v>
       </c>
       <c r="Y16" t="n">
-        <v>641.8744398918423</v>
+        <v>641.8744398918424</v>
       </c>
     </row>
     <row r="17">
@@ -5491,10 +5491,10 @@
         <v>383.4492766736557</v>
       </c>
       <c r="E17" t="n">
-        <v>297.2237316162127</v>
+        <v>297.9268477742883</v>
       </c>
       <c r="F17" t="n">
-        <v>210.4665309010492</v>
+        <v>211.1696470591248</v>
       </c>
       <c r="G17" t="n">
         <v>127.0464193797368</v>
@@ -5506,16 +5506,16 @@
         <v>52.4</v>
       </c>
       <c r="J17" t="n">
-        <v>567.6776741934345</v>
+        <v>141.6759849731395</v>
       </c>
       <c r="K17" t="n">
-        <v>1216.127674193434</v>
+        <v>327.4727226113304</v>
       </c>
       <c r="L17" t="n">
-        <v>1864.577674193434</v>
+        <v>975.9227226113303</v>
       </c>
       <c r="M17" t="n">
-        <v>2233.691587554807</v>
+        <v>1585.241587554807</v>
       </c>
       <c r="N17" t="n">
         <v>2233.691587554807</v>
@@ -5561,7 +5561,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>180.5214748259267</v>
+        <v>502.743697048149</v>
       </c>
       <c r="C18" t="n">
         <v>137.9963107395436</v>
@@ -5609,28 +5609,28 @@
         <v>2313.990605368536</v>
       </c>
       <c r="R18" t="n">
-        <v>1907.723677356515</v>
+        <v>2132.917892265885</v>
       </c>
       <c r="S18" t="n">
-        <v>1773.479928583418</v>
+        <v>1998.674143492788</v>
       </c>
       <c r="T18" t="n">
-        <v>1689.463823065442</v>
+        <v>1914.658037974811</v>
       </c>
       <c r="U18" t="n">
-        <v>1285.26339296653</v>
+        <v>1832.679830098122</v>
       </c>
       <c r="V18" t="n">
-        <v>1188.787971560954</v>
+        <v>1736.204408692546</v>
       </c>
       <c r="W18" t="n">
-        <v>1074.26964538941</v>
+        <v>1621.686082521002</v>
       </c>
       <c r="X18" t="n">
-        <v>650.1658681718469</v>
+        <v>1294.610312616292</v>
       </c>
       <c r="Y18" t="n">
-        <v>246.7402189131253</v>
+        <v>891.1846633575699</v>
       </c>
     </row>
     <row r="19">
@@ -5719,76 +5719,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>607.503553424077</v>
+        <v>608.2066695820786</v>
       </c>
       <c r="C20" t="n">
-        <v>475.7110501483256</v>
+        <v>476.4141663063272</v>
       </c>
       <c r="D20" t="n">
-        <v>383.4492766737299</v>
+        <v>384.1523928317314</v>
       </c>
       <c r="E20" t="n">
-        <v>297.9268477742899</v>
+        <v>297.9268477742883</v>
       </c>
       <c r="F20" t="n">
-        <v>211.1696470591263</v>
+        <v>211.1696470591248</v>
       </c>
       <c r="G20" t="n">
-        <v>127.0464193797383</v>
+        <v>127.0464193797368</v>
       </c>
       <c r="H20" t="n">
-        <v>52.40000000000148</v>
+        <v>52.4</v>
       </c>
       <c r="I20" t="n">
-        <v>52.40000000000148</v>
+        <v>52.4</v>
       </c>
       <c r="J20" t="n">
-        <v>567.677674193436</v>
+        <v>567.6776741934345</v>
       </c>
       <c r="K20" t="n">
-        <v>1216.127674193454</v>
+        <v>1216.127674193434</v>
       </c>
       <c r="L20" t="n">
-        <v>1446.624956505012</v>
+        <v>1446.624956504992</v>
       </c>
       <c r="M20" t="n">
-        <v>1637.361628029852</v>
+        <v>1585.241587554807</v>
       </c>
       <c r="N20" t="n">
-        <v>1637.361628029852</v>
+        <v>2233.691587554807</v>
       </c>
       <c r="O20" t="n">
-        <v>1813.914800116325</v>
+        <v>2410.24475964128</v>
       </c>
       <c r="P20" t="n">
-        <v>2023.670040475045</v>
+        <v>2620</v>
       </c>
       <c r="Q20" t="n">
-        <v>2620.000000000074</v>
+        <v>2620</v>
       </c>
       <c r="R20" t="n">
-        <v>2620.000000000074</v>
+        <v>2620</v>
       </c>
       <c r="S20" t="n">
-        <v>2476.335336314666</v>
+        <v>2477.038452472668</v>
       </c>
       <c r="T20" t="n">
-        <v>2212.479660135872</v>
+        <v>2213.182776293874</v>
       </c>
       <c r="U20" t="n">
-        <v>1879.042017309754</v>
+        <v>1879.745133467756</v>
       </c>
       <c r="V20" t="n">
-        <v>1565.051083807912</v>
+        <v>1565.754199965913</v>
       </c>
       <c r="W20" t="n">
-        <v>1242.451613120086</v>
+        <v>1243.154729278087</v>
       </c>
       <c r="X20" t="n">
-        <v>966.4093570992093</v>
+        <v>967.1124732572108</v>
       </c>
       <c r="Y20" t="n">
-        <v>772.1493240862735</v>
+        <v>772.852440244275</v>
       </c>
     </row>
     <row r="21">
@@ -5798,76 +5798,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>180.5214748259282</v>
+        <v>1147.188141492593</v>
       </c>
       <c r="C21" t="n">
-        <v>137.9963107395451</v>
+        <v>1104.66297740621</v>
       </c>
       <c r="D21" t="n">
-        <v>108.7663239741889</v>
+        <v>753.2107684186319</v>
       </c>
       <c r="E21" t="n">
-        <v>84.8551146591256</v>
+        <v>407.0773368813464</v>
       </c>
       <c r="F21" t="n">
-        <v>64.01042542894696</v>
+        <v>64.01042542894548</v>
       </c>
       <c r="G21" t="n">
-        <v>58.00018335964166</v>
+        <v>58.00018335964016</v>
       </c>
       <c r="H21" t="n">
-        <v>52.40000000000148</v>
+        <v>52.4</v>
       </c>
       <c r="I21" t="n">
-        <v>52.40000000000148</v>
+        <v>52.4</v>
       </c>
       <c r="J21" t="n">
-        <v>250.1913459300174</v>
+        <v>250.191345930016</v>
       </c>
       <c r="K21" t="n">
-        <v>565.579639477231</v>
+        <v>565.5796394772295</v>
       </c>
       <c r="L21" t="n">
-        <v>1006.615493996959</v>
+        <v>1006.615493996958</v>
       </c>
       <c r="M21" t="n">
-        <v>1290.710885739819</v>
+        <v>1290.710885739817</v>
       </c>
       <c r="N21" t="n">
-        <v>1627.246884215311</v>
+        <v>1627.24688421531</v>
       </c>
       <c r="O21" t="n">
-        <v>2052.228604861295</v>
+        <v>2052.228604861293</v>
       </c>
       <c r="P21" t="n">
-        <v>2313.990605368537</v>
+        <v>2313.990605368536</v>
       </c>
       <c r="Q21" t="n">
-        <v>2240.946636437807</v>
+        <v>2313.990605368536</v>
       </c>
       <c r="R21" t="n">
-        <v>1907.723677356517</v>
+        <v>2132.917892265885</v>
       </c>
       <c r="S21" t="n">
-        <v>1773.47992858342</v>
+        <v>1998.674143492788</v>
       </c>
       <c r="T21" t="n">
-        <v>1689.463823065443</v>
+        <v>1914.658037974811</v>
       </c>
       <c r="U21" t="n">
-        <v>1285.263392966532</v>
+        <v>1832.679830098122</v>
       </c>
       <c r="V21" t="n">
-        <v>866.5657493387334</v>
+        <v>1736.204408692546</v>
       </c>
       <c r="W21" t="n">
-        <v>429.8252009449672</v>
+        <v>1621.686082521002</v>
       </c>
       <c r="X21" t="n">
-        <v>327.9436459496262</v>
+        <v>1519.804527525661</v>
       </c>
       <c r="Y21" t="n">
-        <v>246.7402189131268</v>
+        <v>1438.601100489161</v>
       </c>
     </row>
     <row r="22">
@@ -5877,76 +5877,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>673.441777558136</v>
+        <v>673.4417775581345</v>
       </c>
       <c r="C22" t="n">
-        <v>719.2537833765717</v>
+        <v>719.2537833765703</v>
       </c>
       <c r="D22" t="n">
-        <v>752.3829275015718</v>
+        <v>752.3829275015703</v>
       </c>
       <c r="E22" t="n">
-        <v>790.0218317129847</v>
+        <v>790.0218317129833</v>
       </c>
       <c r="F22" t="n">
-        <v>834.1928043049203</v>
+        <v>834.1928043049188</v>
       </c>
       <c r="G22" t="n">
-        <v>908.0645554377072</v>
+        <v>908.0645554377057</v>
       </c>
       <c r="H22" t="n">
-        <v>1003.216333056121</v>
+        <v>1003.21633305612</v>
       </c>
       <c r="I22" t="n">
-        <v>1163.862419205319</v>
+        <v>1163.862419205318</v>
       </c>
       <c r="J22" t="n">
-        <v>1491.077756743016</v>
+        <v>1491.077756743015</v>
       </c>
       <c r="K22" t="n">
-        <v>1597.372803794639</v>
+        <v>1597.372803794637</v>
       </c>
       <c r="L22" t="n">
-        <v>1591.155096928857</v>
+        <v>1591.155096928856</v>
       </c>
       <c r="M22" t="n">
-        <v>1492.275360291077</v>
+        <v>1492.275360291076</v>
       </c>
       <c r="N22" t="n">
-        <v>1339.83988104662</v>
+        <v>1339.839881046618</v>
       </c>
       <c r="O22" t="n">
-        <v>1109.635154952566</v>
+        <v>1109.635154952564</v>
       </c>
       <c r="P22" t="n">
-        <v>818.3161660963825</v>
+        <v>818.3161660963807</v>
       </c>
       <c r="Q22" t="n">
-        <v>463.3441798078997</v>
+        <v>463.3441798078979</v>
       </c>
       <c r="R22" t="n">
-        <v>81.68251716755827</v>
+        <v>81.68251716755651</v>
       </c>
       <c r="S22" t="n">
-        <v>52.40000000000148</v>
+        <v>52.4</v>
       </c>
       <c r="T22" t="n">
-        <v>163.0851070276588</v>
+        <v>163.0851070276573</v>
       </c>
       <c r="U22" t="n">
-        <v>329.4820370429946</v>
+        <v>329.4820370429932</v>
       </c>
       <c r="V22" t="n">
-        <v>448.1134299289406</v>
+        <v>448.1134299289391</v>
       </c>
       <c r="W22" t="n">
-        <v>539.8143481886181</v>
+        <v>539.8143481886166</v>
       </c>
       <c r="X22" t="n">
-        <v>610.6551392128116</v>
+        <v>610.6551392128101</v>
       </c>
       <c r="Y22" t="n">
-        <v>641.8744398918438</v>
+        <v>641.8744398918424</v>
       </c>
     </row>
     <row r="23">
@@ -5956,76 +5956,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>607.503553424077</v>
+        <v>608.2066695820786</v>
       </c>
       <c r="C23" t="n">
-        <v>475.7110501483256</v>
+        <v>476.4141663063272</v>
       </c>
       <c r="D23" t="n">
-        <v>383.4492766737299</v>
+        <v>384.1523928317314</v>
       </c>
       <c r="E23" t="n">
-        <v>297.2237316162868</v>
+        <v>297.9268477742883</v>
       </c>
       <c r="F23" t="n">
-        <v>210.4665309011233</v>
+        <v>211.1696470591248</v>
       </c>
       <c r="G23" t="n">
-        <v>127.0464193797383</v>
+        <v>127.0464193797368</v>
       </c>
       <c r="H23" t="n">
-        <v>52.40000000000148</v>
+        <v>52.4</v>
       </c>
       <c r="I23" t="n">
-        <v>52.40000000000148</v>
+        <v>52.4</v>
       </c>
       <c r="J23" t="n">
-        <v>567.677674193436</v>
+        <v>567.6776741934345</v>
       </c>
       <c r="K23" t="n">
-        <v>753.4744118316269</v>
+        <v>1216.127674193434</v>
       </c>
       <c r="L23" t="n">
-        <v>983.9716941431847</v>
+        <v>1446.624956504992</v>
       </c>
       <c r="M23" t="n">
-        <v>988.9116280298445</v>
+        <v>1585.241587554807</v>
       </c>
       <c r="N23" t="n">
-        <v>1637.361628029852</v>
+        <v>2233.691587554807</v>
       </c>
       <c r="O23" t="n">
-        <v>1813.914800116325</v>
+        <v>2410.244759641279</v>
       </c>
       <c r="P23" t="n">
-        <v>2023.670040475045</v>
+        <v>2620</v>
       </c>
       <c r="Q23" t="n">
-        <v>2620.000000000074</v>
+        <v>2620</v>
       </c>
       <c r="R23" t="n">
-        <v>2620.000000000074</v>
+        <v>2620</v>
       </c>
       <c r="S23" t="n">
-        <v>2476.335336314666</v>
+        <v>2477.038452472668</v>
       </c>
       <c r="T23" t="n">
-        <v>2212.479660135872</v>
+        <v>2213.182776293874</v>
       </c>
       <c r="U23" t="n">
-        <v>1879.042017309754</v>
+        <v>1879.745133467756</v>
       </c>
       <c r="V23" t="n">
-        <v>1565.051083807912</v>
+        <v>1565.754199965913</v>
       </c>
       <c r="W23" t="n">
-        <v>1242.451613120086</v>
+        <v>1243.154729278087</v>
       </c>
       <c r="X23" t="n">
-        <v>966.4093570992093</v>
+        <v>967.1124732572108</v>
       </c>
       <c r="Y23" t="n">
-        <v>772.1493240862735</v>
+        <v>772.852440244275</v>
       </c>
     </row>
     <row r="24">
@@ -6035,76 +6035,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>180.5214748259282</v>
+        <v>1147.188141492594</v>
       </c>
       <c r="C24" t="n">
-        <v>137.9963107395451</v>
+        <v>782.4407551839881</v>
       </c>
       <c r="D24" t="n">
-        <v>108.7663239741889</v>
+        <v>430.9885461964097</v>
       </c>
       <c r="E24" t="n">
-        <v>84.8551146591256</v>
+        <v>407.0773368813464</v>
       </c>
       <c r="F24" t="n">
-        <v>64.01042542894696</v>
+        <v>64.01042542894548</v>
       </c>
       <c r="G24" t="n">
-        <v>58.00018335964165</v>
+        <v>58.00018335964018</v>
       </c>
       <c r="H24" t="n">
-        <v>52.40000000000148</v>
+        <v>52.4</v>
       </c>
       <c r="I24" t="n">
-        <v>52.40000000000148</v>
+        <v>52.4</v>
       </c>
       <c r="J24" t="n">
-        <v>250.1913459300174</v>
+        <v>250.191345930016</v>
       </c>
       <c r="K24" t="n">
-        <v>565.579639477231</v>
+        <v>565.5796394772295</v>
       </c>
       <c r="L24" t="n">
-        <v>1006.615493996959</v>
+        <v>1006.615493996958</v>
       </c>
       <c r="M24" t="n">
-        <v>1290.710885739819</v>
+        <v>1290.710885739817</v>
       </c>
       <c r="N24" t="n">
-        <v>1627.246884215311</v>
+        <v>1627.24688421531</v>
       </c>
       <c r="O24" t="n">
-        <v>2052.228604861295</v>
+        <v>2052.228604861293</v>
       </c>
       <c r="P24" t="n">
-        <v>2313.990605368537</v>
+        <v>2313.990605368536</v>
       </c>
       <c r="Q24" t="n">
-        <v>2240.946636437807</v>
+        <v>2313.990605368536</v>
       </c>
       <c r="R24" t="n">
-        <v>2059.873923335156</v>
+        <v>2132.917892265885</v>
       </c>
       <c r="S24" t="n">
-        <v>1925.630174562059</v>
+        <v>1998.674143492788</v>
       </c>
       <c r="T24" t="n">
-        <v>1841.614069044082</v>
+        <v>1914.658037974811</v>
       </c>
       <c r="U24" t="n">
-        <v>1607.485615188754</v>
+        <v>1832.679830098122</v>
       </c>
       <c r="V24" t="n">
-        <v>1511.010193783178</v>
+        <v>1736.204408692546</v>
       </c>
       <c r="W24" t="n">
-        <v>1074.269645389412</v>
+        <v>1396.491867611632</v>
       </c>
       <c r="X24" t="n">
-        <v>650.1658681718484</v>
+        <v>1294.610312616291</v>
       </c>
       <c r="Y24" t="n">
-        <v>246.7402189131268</v>
+        <v>1213.406885579792</v>
       </c>
     </row>
     <row r="25">
@@ -6114,76 +6114,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>673.441777558136</v>
+        <v>673.4417775581344</v>
       </c>
       <c r="C25" t="n">
-        <v>719.2537833765717</v>
+        <v>719.2537833765701</v>
       </c>
       <c r="D25" t="n">
-        <v>752.3829275015718</v>
+        <v>752.3829275015702</v>
       </c>
       <c r="E25" t="n">
-        <v>790.0218317129847</v>
+        <v>790.0218317129832</v>
       </c>
       <c r="F25" t="n">
-        <v>834.1928043049203</v>
+        <v>834.1928043049187</v>
       </c>
       <c r="G25" t="n">
-        <v>908.0645554377072</v>
+        <v>908.0645554377056</v>
       </c>
       <c r="H25" t="n">
-        <v>1003.216333056121</v>
+        <v>1003.21633305612</v>
       </c>
       <c r="I25" t="n">
-        <v>1163.862419205319</v>
+        <v>1163.862419205317</v>
       </c>
       <c r="J25" t="n">
-        <v>1491.077756743016</v>
+        <v>1491.077756743014</v>
       </c>
       <c r="K25" t="n">
-        <v>1597.372803794639</v>
+        <v>1597.372803794637</v>
       </c>
       <c r="L25" t="n">
-        <v>1591.155096928857</v>
+        <v>1591.155096928856</v>
       </c>
       <c r="M25" t="n">
-        <v>1492.275360291077</v>
+        <v>1492.275360291075</v>
       </c>
       <c r="N25" t="n">
-        <v>1339.83988104662</v>
+        <v>1342.71903405416</v>
       </c>
       <c r="O25" t="n">
-        <v>1109.635154952566</v>
+        <v>1112.514307960106</v>
       </c>
       <c r="P25" t="n">
-        <v>818.3161660963821</v>
+        <v>821.1953191039224</v>
       </c>
       <c r="Q25" t="n">
-        <v>463.3441798078993</v>
+        <v>466.2233328154397</v>
       </c>
       <c r="R25" t="n">
-        <v>81.68251716755788</v>
+        <v>84.56167017509823</v>
       </c>
       <c r="S25" t="n">
-        <v>52.40000000000148</v>
+        <v>52.4</v>
       </c>
       <c r="T25" t="n">
-        <v>163.0851070276588</v>
+        <v>163.0851070276573</v>
       </c>
       <c r="U25" t="n">
-        <v>329.4820370429946</v>
+        <v>329.4820370429931</v>
       </c>
       <c r="V25" t="n">
-        <v>448.1134299289406</v>
+        <v>448.1134299289391</v>
       </c>
       <c r="W25" t="n">
-        <v>539.8143481886181</v>
+        <v>539.8143481886165</v>
       </c>
       <c r="X25" t="n">
-        <v>610.6551392128116</v>
+        <v>610.65513921281</v>
       </c>
       <c r="Y25" t="n">
-        <v>641.8744398918438</v>
+        <v>641.8744398918423</v>
       </c>
     </row>
     <row r="26">
@@ -6193,76 +6193,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>607.5035534240761</v>
+        <v>608.2066695820786</v>
       </c>
       <c r="C26" t="n">
-        <v>475.7110501483247</v>
+        <v>476.4141663063272</v>
       </c>
       <c r="D26" t="n">
-        <v>383.4492766737289</v>
+        <v>384.1523928317314</v>
       </c>
       <c r="E26" t="n">
-        <v>297.2237316162859</v>
+        <v>297.9268477742883</v>
       </c>
       <c r="F26" t="n">
-        <v>210.4665309011224</v>
+        <v>211.1696470591248</v>
       </c>
       <c r="G26" t="n">
-        <v>127.0464193797383</v>
+        <v>127.0464193797368</v>
       </c>
       <c r="H26" t="n">
-        <v>52.40000000000146</v>
+        <v>52.4</v>
       </c>
       <c r="I26" t="n">
-        <v>52.40000000000146</v>
+        <v>52.4</v>
       </c>
       <c r="J26" t="n">
-        <v>567.677674193436</v>
+        <v>141.6759849731395</v>
       </c>
       <c r="K26" t="n">
-        <v>753.4744118316269</v>
+        <v>327.4727226113304</v>
       </c>
       <c r="L26" t="n">
-        <v>983.9716941431847</v>
+        <v>557.9700049228883</v>
       </c>
       <c r="M26" t="n">
-        <v>988.9116280298401</v>
+        <v>1206.42000492289</v>
       </c>
       <c r="N26" t="n">
-        <v>1637.361628029851</v>
+        <v>1206.42000492289</v>
       </c>
       <c r="O26" t="n">
-        <v>1813.914800116324</v>
+        <v>1382.973177009363</v>
       </c>
       <c r="P26" t="n">
-        <v>2023.670040475044</v>
+        <v>2023.670040474971</v>
       </c>
       <c r="Q26" t="n">
-        <v>2620.000000000073</v>
+        <v>2620</v>
       </c>
       <c r="R26" t="n">
-        <v>2620.000000000073</v>
+        <v>2620.000000000022</v>
       </c>
       <c r="S26" t="n">
-        <v>2476.335336314665</v>
+        <v>2476.335336314614</v>
       </c>
       <c r="T26" t="n">
-        <v>2212.479660135871</v>
+        <v>2212.47966013582</v>
       </c>
       <c r="U26" t="n">
-        <v>1879.042017309753</v>
+        <v>1879.042017309702</v>
       </c>
       <c r="V26" t="n">
-        <v>1565.051083807911</v>
+        <v>1565.754199965913</v>
       </c>
       <c r="W26" t="n">
-        <v>1242.451613120085</v>
+        <v>1243.154729278087</v>
       </c>
       <c r="X26" t="n">
-        <v>966.4093570992084</v>
+        <v>967.1124732572108</v>
       </c>
       <c r="Y26" t="n">
-        <v>772.1493240862726</v>
+        <v>772.852440244275</v>
       </c>
     </row>
     <row r="27">
@@ -6272,76 +6272,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1147.188141492595</v>
+        <v>694.609972105162</v>
       </c>
       <c r="C27" t="n">
-        <v>782.4407551839895</v>
+        <v>329.8625857965566</v>
       </c>
       <c r="D27" t="n">
-        <v>430.9885461964111</v>
+        <v>300.6325990312004</v>
       </c>
       <c r="E27" t="n">
-        <v>407.0773368813478</v>
+        <v>276.7213897161371</v>
       </c>
       <c r="F27" t="n">
-        <v>386.2326476511691</v>
+        <v>255.8767004859585</v>
       </c>
       <c r="G27" t="n">
-        <v>58.00018335964162</v>
+        <v>249.8664584166532</v>
       </c>
       <c r="H27" t="n">
-        <v>52.40000000000146</v>
+        <v>244.266275057013</v>
       </c>
       <c r="I27" t="n">
-        <v>52.40000000000146</v>
+        <v>52.4</v>
       </c>
       <c r="J27" t="n">
-        <v>250.1913459300174</v>
+        <v>250.191345930016</v>
       </c>
       <c r="K27" t="n">
-        <v>565.579639477231</v>
+        <v>565.5796394772295</v>
       </c>
       <c r="L27" t="n">
-        <v>1006.615493996959</v>
+        <v>1006.615493996958</v>
       </c>
       <c r="M27" t="n">
-        <v>1290.710885739819</v>
+        <v>1290.710885739817</v>
       </c>
       <c r="N27" t="n">
-        <v>1627.246884215311</v>
+        <v>1627.24688421531</v>
       </c>
       <c r="O27" t="n">
-        <v>2052.228604861295</v>
+        <v>2052.228604861293</v>
       </c>
       <c r="P27" t="n">
-        <v>2313.990605368537</v>
+        <v>2313.990605368536</v>
       </c>
       <c r="Q27" t="n">
-        <v>2313.990605368537</v>
+        <v>2313.990605368536</v>
       </c>
       <c r="R27" t="n">
-        <v>2132.917892265886</v>
+        <v>2132.917892265885</v>
       </c>
       <c r="S27" t="n">
-        <v>1773.47992858342</v>
+        <v>1998.674143492788</v>
       </c>
       <c r="T27" t="n">
-        <v>1689.463823065443</v>
+        <v>1881.330098122455</v>
       </c>
       <c r="U27" t="n">
-        <v>1607.485615188754</v>
+        <v>1477.129668023543</v>
       </c>
       <c r="V27" t="n">
-        <v>1511.010193783178</v>
+        <v>1380.654246617967</v>
       </c>
       <c r="W27" t="n">
-        <v>1396.491867611634</v>
+        <v>1266.135920446423</v>
       </c>
       <c r="X27" t="n">
-        <v>1294.610312616293</v>
+        <v>842.0321432288599</v>
       </c>
       <c r="Y27" t="n">
-        <v>1213.406885579793</v>
+        <v>760.8287161923606</v>
       </c>
     </row>
     <row r="28">
@@ -6351,76 +6351,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>673.4417775581359</v>
+        <v>673.4417775581345</v>
       </c>
       <c r="C28" t="n">
-        <v>719.2537833765716</v>
+        <v>719.2537833765703</v>
       </c>
       <c r="D28" t="n">
-        <v>752.3829275015717</v>
+        <v>752.3829275015703</v>
       </c>
       <c r="E28" t="n">
-        <v>790.0218317129846</v>
+        <v>790.0218317129833</v>
       </c>
       <c r="F28" t="n">
-        <v>834.1928043049202</v>
+        <v>834.1928043049188</v>
       </c>
       <c r="G28" t="n">
-        <v>908.0645554377071</v>
+        <v>908.0645554377057</v>
       </c>
       <c r="H28" t="n">
-        <v>1003.216333056121</v>
+        <v>1003.21633305612</v>
       </c>
       <c r="I28" t="n">
-        <v>1163.862419205319</v>
+        <v>1163.862419205318</v>
       </c>
       <c r="J28" t="n">
-        <v>1491.077756743016</v>
+        <v>1491.077756743015</v>
       </c>
       <c r="K28" t="n">
-        <v>1597.372803794639</v>
+        <v>1597.372803794637</v>
       </c>
       <c r="L28" t="n">
-        <v>1594.034249936399</v>
+        <v>1594.034249936398</v>
       </c>
       <c r="M28" t="n">
-        <v>1495.154513298619</v>
+        <v>1495.154513298618</v>
       </c>
       <c r="N28" t="n">
-        <v>1342.719034054162</v>
+        <v>1342.71903405416</v>
       </c>
       <c r="O28" t="n">
-        <v>1112.514307960108</v>
+        <v>1112.514307960106</v>
       </c>
       <c r="P28" t="n">
-        <v>821.1953191039239</v>
+        <v>821.1953191039224</v>
       </c>
       <c r="Q28" t="n">
-        <v>466.2233328154411</v>
+        <v>466.2233328154396</v>
       </c>
       <c r="R28" t="n">
-        <v>84.56167017509972</v>
+        <v>84.56167017509824</v>
       </c>
       <c r="S28" t="n">
-        <v>52.40000000000146</v>
+        <v>52.4</v>
       </c>
       <c r="T28" t="n">
-        <v>163.0851070276588</v>
+        <v>163.0851070276573</v>
       </c>
       <c r="U28" t="n">
-        <v>329.4820370429946</v>
+        <v>329.4820370429932</v>
       </c>
       <c r="V28" t="n">
-        <v>448.1134299289405</v>
+        <v>448.1134299289391</v>
       </c>
       <c r="W28" t="n">
-        <v>539.8143481886179</v>
+        <v>539.8143481886166</v>
       </c>
       <c r="X28" t="n">
-        <v>610.6551392128115</v>
+        <v>610.6551392128101</v>
       </c>
       <c r="Y28" t="n">
-        <v>641.8744398918437</v>
+        <v>641.8744398918424</v>
       </c>
     </row>
     <row r="29">
@@ -6430,76 +6430,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>607.5035534240716</v>
+        <v>608.2066695820786</v>
       </c>
       <c r="C29" t="n">
-        <v>475.7110501483202</v>
+        <v>476.4141663063272</v>
       </c>
       <c r="D29" t="n">
-        <v>383.4492766737244</v>
+        <v>384.1523928317314</v>
       </c>
       <c r="E29" t="n">
-        <v>297.2237316162813</v>
+        <v>297.9268477742883</v>
       </c>
       <c r="F29" t="n">
-        <v>210.4665309011178</v>
+        <v>211.1696470591248</v>
       </c>
       <c r="G29" t="n">
-        <v>127.0464193797383</v>
+        <v>127.0464193797368</v>
       </c>
       <c r="H29" t="n">
-        <v>52.40000000000146</v>
+        <v>52.4</v>
       </c>
       <c r="I29" t="n">
-        <v>52.40000000000146</v>
+        <v>52.4</v>
       </c>
       <c r="J29" t="n">
-        <v>141.6759849731409</v>
+        <v>141.6759849731395</v>
       </c>
       <c r="K29" t="n">
-        <v>790.125984973159</v>
+        <v>327.4727226113304</v>
       </c>
       <c r="L29" t="n">
-        <v>1438.575984973177</v>
+        <v>557.9700049228883</v>
       </c>
       <c r="M29" t="n">
-        <v>1585.241587554859</v>
+        <v>988.9116280297721</v>
       </c>
       <c r="N29" t="n">
-        <v>2233.691587554876</v>
+        <v>1637.361628029778</v>
       </c>
       <c r="O29" t="n">
-        <v>2410.244759641348</v>
+        <v>1813.91480011625</v>
       </c>
       <c r="P29" t="n">
-        <v>2620.000000000069</v>
+        <v>2023.670040474971</v>
       </c>
       <c r="Q29" t="n">
-        <v>2620.000000000069</v>
+        <v>2620</v>
       </c>
       <c r="R29" t="n">
-        <v>2620.000000000069</v>
+        <v>2620</v>
       </c>
       <c r="S29" t="n">
-        <v>2476.335336314661</v>
+        <v>2476.335336314592</v>
       </c>
       <c r="T29" t="n">
-        <v>2212.479660135867</v>
+        <v>2212.479660135798</v>
       </c>
       <c r="U29" t="n">
-        <v>1879.042017309749</v>
+        <v>1879.745133467756</v>
       </c>
       <c r="V29" t="n">
-        <v>1565.051083807906</v>
+        <v>1565.754199965913</v>
       </c>
       <c r="W29" t="n">
-        <v>1242.45161312008</v>
+        <v>1243.154729278087</v>
       </c>
       <c r="X29" t="n">
-        <v>966.4093570992038</v>
+        <v>967.1124732572108</v>
       </c>
       <c r="Y29" t="n">
-        <v>772.1493240862681</v>
+        <v>772.852440244275</v>
       </c>
     </row>
     <row r="30">
@@ -6509,76 +6509,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1147.188141492595</v>
+        <v>180.5214748259267</v>
       </c>
       <c r="C30" t="n">
-        <v>782.4407551839895</v>
+        <v>137.9963107395436</v>
       </c>
       <c r="D30" t="n">
-        <v>430.9885461964111</v>
+        <v>108.7663239741874</v>
       </c>
       <c r="E30" t="n">
-        <v>84.8551146591256</v>
+        <v>84.85511465912413</v>
       </c>
       <c r="F30" t="n">
-        <v>64.01042542894695</v>
+        <v>64.01042542894548</v>
       </c>
       <c r="G30" t="n">
-        <v>58.00018335964164</v>
+        <v>58.00018335964016</v>
       </c>
       <c r="H30" t="n">
-        <v>52.40000000000146</v>
+        <v>52.4</v>
       </c>
       <c r="I30" t="n">
-        <v>52.40000000000146</v>
+        <v>52.4</v>
       </c>
       <c r="J30" t="n">
-        <v>250.1913459300174</v>
+        <v>250.191345930016</v>
       </c>
       <c r="K30" t="n">
-        <v>565.579639477231</v>
+        <v>565.5796394772295</v>
       </c>
       <c r="L30" t="n">
-        <v>1006.615493996959</v>
+        <v>1006.615493996958</v>
       </c>
       <c r="M30" t="n">
-        <v>1290.710885739819</v>
+        <v>1290.710885739817</v>
       </c>
       <c r="N30" t="n">
-        <v>1627.246884215311</v>
+        <v>1627.24688421531</v>
       </c>
       <c r="O30" t="n">
-        <v>2052.228604861295</v>
+        <v>2052.228604861293</v>
       </c>
       <c r="P30" t="n">
-        <v>2313.990605368537</v>
+        <v>2313.990605368536</v>
       </c>
       <c r="Q30" t="n">
-        <v>2313.990605368537</v>
+        <v>2313.990605368536</v>
       </c>
       <c r="R30" t="n">
-        <v>2132.917892265886</v>
+        <v>2132.917892265885</v>
       </c>
       <c r="S30" t="n">
-        <v>1998.674143492789</v>
+        <v>1998.674143492788</v>
       </c>
       <c r="T30" t="n">
-        <v>1914.658037974812</v>
+        <v>1914.658037974811</v>
       </c>
       <c r="U30" t="n">
-        <v>1832.679830098123</v>
+        <v>1607.485615188752</v>
       </c>
       <c r="V30" t="n">
-        <v>1736.204408692547</v>
+        <v>1188.787971560954</v>
       </c>
       <c r="W30" t="n">
-        <v>1621.686082521003</v>
+        <v>752.0474231671878</v>
       </c>
       <c r="X30" t="n">
-        <v>1519.804527525662</v>
+        <v>327.9436459496247</v>
       </c>
       <c r="Y30" t="n">
-        <v>1438.601100489163</v>
+        <v>246.7402189131253</v>
       </c>
     </row>
     <row r="31">
@@ -6588,76 +6588,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>673.4417775581359</v>
+        <v>673.4417775581345</v>
       </c>
       <c r="C31" t="n">
-        <v>719.2537833765716</v>
+        <v>719.2537833765703</v>
       </c>
       <c r="D31" t="n">
-        <v>752.3829275015717</v>
+        <v>752.3829275015703</v>
       </c>
       <c r="E31" t="n">
-        <v>790.0218317129846</v>
+        <v>790.0218317129833</v>
       </c>
       <c r="F31" t="n">
-        <v>834.1928043049202</v>
+        <v>834.1928043049188</v>
       </c>
       <c r="G31" t="n">
-        <v>908.0645554377071</v>
+        <v>908.0645554377057</v>
       </c>
       <c r="H31" t="n">
-        <v>1003.216333056121</v>
+        <v>1003.21633305612</v>
       </c>
       <c r="I31" t="n">
-        <v>1163.862419205319</v>
+        <v>1163.862419205318</v>
       </c>
       <c r="J31" t="n">
-        <v>1491.077756743016</v>
+        <v>1491.077756743015</v>
       </c>
       <c r="K31" t="n">
-        <v>1597.372803794639</v>
+        <v>1597.372803794637</v>
       </c>
       <c r="L31" t="n">
-        <v>1594.034249936399</v>
+        <v>1591.155096928856</v>
       </c>
       <c r="M31" t="n">
-        <v>1495.154513298619</v>
+        <v>1492.275360291076</v>
       </c>
       <c r="N31" t="n">
-        <v>1342.719034054162</v>
+        <v>1339.839881046618</v>
       </c>
       <c r="O31" t="n">
-        <v>1112.514307960108</v>
+        <v>1109.635154952564</v>
       </c>
       <c r="P31" t="n">
-        <v>821.195319103924</v>
+        <v>818.3161660963807</v>
       </c>
       <c r="Q31" t="n">
-        <v>466.2233328154412</v>
+        <v>463.3441798078979</v>
       </c>
       <c r="R31" t="n">
-        <v>84.56167017509969</v>
+        <v>81.68251716755651</v>
       </c>
       <c r="S31" t="n">
-        <v>52.40000000000146</v>
+        <v>52.4</v>
       </c>
       <c r="T31" t="n">
-        <v>163.0851070276588</v>
+        <v>163.0851070276573</v>
       </c>
       <c r="U31" t="n">
-        <v>329.4820370429946</v>
+        <v>329.4820370429932</v>
       </c>
       <c r="V31" t="n">
-        <v>448.1134299289405</v>
+        <v>448.1134299289391</v>
       </c>
       <c r="W31" t="n">
-        <v>539.8143481886179</v>
+        <v>539.8143481886166</v>
       </c>
       <c r="X31" t="n">
-        <v>610.6551392128115</v>
+        <v>610.6551392128101</v>
       </c>
       <c r="Y31" t="n">
-        <v>641.8744398918437</v>
+        <v>641.8744398918424</v>
       </c>
     </row>
     <row r="32">
@@ -6667,52 +6667,52 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>608.2066695820801</v>
+        <v>607.5035534240761</v>
       </c>
       <c r="C32" t="n">
-        <v>476.4141663063286</v>
+        <v>475.7110501483247</v>
       </c>
       <c r="D32" t="n">
-        <v>384.1523928317329</v>
+        <v>383.4492766737289</v>
       </c>
       <c r="E32" t="n">
-        <v>297.9268477742898</v>
+        <v>297.2237316162859</v>
       </c>
       <c r="F32" t="n">
-        <v>211.1696470591263</v>
+        <v>210.4665309011224</v>
       </c>
       <c r="G32" t="n">
-        <v>127.0464193797383</v>
+        <v>126.3433032217344</v>
       </c>
       <c r="H32" t="n">
-        <v>52.40000000000146</v>
+        <v>52.4</v>
       </c>
       <c r="I32" t="n">
-        <v>52.40000000000146</v>
+        <v>52.4</v>
       </c>
       <c r="J32" t="n">
-        <v>141.6759849731409</v>
+        <v>141.6759849731395</v>
       </c>
       <c r="K32" t="n">
-        <v>327.4727226113318</v>
+        <v>327.4727226113304</v>
       </c>
       <c r="L32" t="n">
-        <v>557.9700049228896</v>
+        <v>975.9227226113303</v>
       </c>
       <c r="M32" t="n">
-        <v>1113.344759641302</v>
+        <v>1624.372722611341</v>
       </c>
       <c r="N32" t="n">
-        <v>1761.794759641327</v>
+        <v>1637.361628029778</v>
       </c>
       <c r="O32" t="n">
-        <v>2410.244759641353</v>
+        <v>1813.91480011625</v>
       </c>
       <c r="P32" t="n">
-        <v>2620.000000000073</v>
+        <v>2023.670040474971</v>
       </c>
       <c r="Q32" t="n">
-        <v>2620.000000000073</v>
+        <v>2620</v>
       </c>
       <c r="R32" t="n">
         <v>2620.000000000073</v>
@@ -6721,22 +6721,22 @@
         <v>2476.335336314665</v>
       </c>
       <c r="T32" t="n">
-        <v>2213.182776293875</v>
+        <v>2212.479660135871</v>
       </c>
       <c r="U32" t="n">
-        <v>1879.745133467757</v>
+        <v>1879.042017309753</v>
       </c>
       <c r="V32" t="n">
-        <v>1565.754199965915</v>
+        <v>1565.051083807911</v>
       </c>
       <c r="W32" t="n">
-        <v>1243.154729278089</v>
+        <v>1242.451613120085</v>
       </c>
       <c r="X32" t="n">
-        <v>967.1124732572123</v>
+        <v>966.4093570992084</v>
       </c>
       <c r="Y32" t="n">
-        <v>772.8524402442765</v>
+        <v>772.1493240862726</v>
       </c>
     </row>
     <row r="33">
@@ -6746,76 +6746,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1372.382356401964</v>
+        <v>1147.188141492593</v>
       </c>
       <c r="C33" t="n">
-        <v>1104.662977406212</v>
+        <v>1104.66297740621</v>
       </c>
       <c r="D33" t="n">
-        <v>753.2107684186333</v>
+        <v>753.2107684186319</v>
       </c>
       <c r="E33" t="n">
-        <v>407.0773368813478</v>
+        <v>407.0773368813464</v>
       </c>
       <c r="F33" t="n">
-        <v>64.01042542894695</v>
+        <v>64.01042542894548</v>
       </c>
       <c r="G33" t="n">
-        <v>58.00018335964164</v>
+        <v>58.00018335964018</v>
       </c>
       <c r="H33" t="n">
-        <v>52.40000000000146</v>
+        <v>52.4</v>
       </c>
       <c r="I33" t="n">
-        <v>52.40000000000146</v>
+        <v>52.4</v>
       </c>
       <c r="J33" t="n">
-        <v>250.1913459300174</v>
+        <v>250.191345930016</v>
       </c>
       <c r="K33" t="n">
-        <v>565.579639477231</v>
+        <v>565.5796394772295</v>
       </c>
       <c r="L33" t="n">
-        <v>1006.615493996959</v>
+        <v>1006.615493996958</v>
       </c>
       <c r="M33" t="n">
-        <v>1290.710885739819</v>
+        <v>1290.710885739817</v>
       </c>
       <c r="N33" t="n">
-        <v>1627.246884215311</v>
+        <v>1627.24688421531</v>
       </c>
       <c r="O33" t="n">
-        <v>2052.228604861295</v>
+        <v>2052.228604861293</v>
       </c>
       <c r="P33" t="n">
-        <v>2313.990605368537</v>
+        <v>2313.990605368536</v>
       </c>
       <c r="Q33" t="n">
-        <v>2313.990605368537</v>
+        <v>2240.946636437805</v>
       </c>
       <c r="R33" t="n">
-        <v>2132.917892265886</v>
+        <v>2059.873923335154</v>
       </c>
       <c r="S33" t="n">
-        <v>1998.674143492789</v>
+        <v>1925.630174562057</v>
       </c>
       <c r="T33" t="n">
-        <v>1914.658037974812</v>
+        <v>1841.614069044081</v>
       </c>
       <c r="U33" t="n">
-        <v>1832.679830098123</v>
+        <v>1759.635861167391</v>
       </c>
       <c r="V33" t="n">
-        <v>1736.204408692547</v>
+        <v>1663.160439761815</v>
       </c>
       <c r="W33" t="n">
-        <v>1621.686082521003</v>
+        <v>1548.642113590271</v>
       </c>
       <c r="X33" t="n">
-        <v>1519.804527525662</v>
+        <v>1446.76055859493</v>
       </c>
       <c r="Y33" t="n">
-        <v>1438.601100489163</v>
+        <v>1365.557131558431</v>
       </c>
     </row>
     <row r="34">
@@ -6825,76 +6825,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>673.4417775581359</v>
+        <v>673.4417775581344</v>
       </c>
       <c r="C34" t="n">
-        <v>719.2537833765716</v>
+        <v>719.2537833765701</v>
       </c>
       <c r="D34" t="n">
-        <v>752.3829275015717</v>
+        <v>752.3829275015702</v>
       </c>
       <c r="E34" t="n">
-        <v>790.0218317129846</v>
+        <v>790.0218317129832</v>
       </c>
       <c r="F34" t="n">
-        <v>834.1928043049202</v>
+        <v>834.1928043049187</v>
       </c>
       <c r="G34" t="n">
-        <v>908.0645554377071</v>
+        <v>908.0645554377056</v>
       </c>
       <c r="H34" t="n">
-        <v>1003.216333056121</v>
+        <v>1003.21633305612</v>
       </c>
       <c r="I34" t="n">
-        <v>1163.862419205319</v>
+        <v>1163.862419205317</v>
       </c>
       <c r="J34" t="n">
-        <v>1491.077756743016</v>
+        <v>1491.077756743014</v>
       </c>
       <c r="K34" t="n">
-        <v>1597.372803794639</v>
+        <v>1597.372803794637</v>
       </c>
       <c r="L34" t="n">
-        <v>1591.155096928857</v>
+        <v>1594.034249936398</v>
       </c>
       <c r="M34" t="n">
-        <v>1492.275360291077</v>
+        <v>1495.154513298618</v>
       </c>
       <c r="N34" t="n">
-        <v>1339.83988104662</v>
+        <v>1342.71903405416</v>
       </c>
       <c r="O34" t="n">
-        <v>1109.635154952566</v>
+        <v>1112.514307960106</v>
       </c>
       <c r="P34" t="n">
-        <v>818.3161660963825</v>
+        <v>821.1953191039224</v>
       </c>
       <c r="Q34" t="n">
-        <v>466.2233328154412</v>
+        <v>466.2233328154397</v>
       </c>
       <c r="R34" t="n">
-        <v>84.56167017509969</v>
+        <v>84.56167017509823</v>
       </c>
       <c r="S34" t="n">
-        <v>52.40000000000146</v>
+        <v>52.4</v>
       </c>
       <c r="T34" t="n">
-        <v>163.0851070276588</v>
+        <v>163.0851070276573</v>
       </c>
       <c r="U34" t="n">
-        <v>329.4820370429946</v>
+        <v>329.4820370429931</v>
       </c>
       <c r="V34" t="n">
-        <v>448.1134299289405</v>
+        <v>448.1134299289391</v>
       </c>
       <c r="W34" t="n">
-        <v>539.8143481886179</v>
+        <v>539.8143481886165</v>
       </c>
       <c r="X34" t="n">
-        <v>610.6551392128115</v>
+        <v>610.65513921281</v>
       </c>
       <c r="Y34" t="n">
-        <v>641.8744398918437</v>
+        <v>641.8744398918423</v>
       </c>
     </row>
     <row r="35">
@@ -6904,76 +6904,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>117.1408562629493</v>
+        <v>117.1408562629478</v>
       </c>
       <c r="C35" t="n">
-        <v>64.13623177507661</v>
+        <v>64.13623177507515</v>
       </c>
       <c r="D35" t="n">
-        <v>50.66233708835965</v>
+        <v>50.66233708835819</v>
       </c>
       <c r="E35" t="n">
-        <v>43.22467081879536</v>
+        <v>43.2246708187939</v>
       </c>
       <c r="F35" t="n">
-        <v>35.25534889151066</v>
+        <v>35.25534889150919</v>
       </c>
       <c r="G35" t="n">
-        <v>29.92000000000147</v>
+        <v>29.92</v>
       </c>
       <c r="H35" t="n">
-        <v>29.92000000000147</v>
+        <v>29.92</v>
       </c>
       <c r="I35" t="n">
-        <v>29.92000000000147</v>
+        <v>29.92</v>
       </c>
       <c r="J35" t="n">
-        <v>119.195984973141</v>
+        <v>119.1959849731395</v>
       </c>
       <c r="K35" t="n">
-        <v>489.455984973159</v>
+        <v>304.9927226113305</v>
       </c>
       <c r="L35" t="n">
-        <v>719.9532672847168</v>
+        <v>535.4900049228883</v>
       </c>
       <c r="M35" t="n">
-        <v>739.4315875548316</v>
+        <v>739.43158755478</v>
       </c>
       <c r="N35" t="n">
-        <v>1109.69158755488</v>
+        <v>1109.691587554807</v>
       </c>
       <c r="O35" t="n">
-        <v>1286.244759641353</v>
+        <v>1286.24475964128</v>
       </c>
       <c r="P35" t="n">
-        <v>1496.000000000073</v>
+        <v>1496</v>
       </c>
       <c r="Q35" t="n">
-        <v>1496.000000000073</v>
+        <v>1496</v>
       </c>
       <c r="R35" t="n">
-        <v>1496.000000000073</v>
+        <v>1496</v>
       </c>
       <c r="S35" t="n">
-        <v>1434.457487638387</v>
+        <v>1431.123215102471</v>
       </c>
       <c r="T35" t="n">
-        <v>1249.389690247471</v>
+        <v>1249.38969024747</v>
       </c>
       <c r="U35" t="n">
-        <v>994.7399262092321</v>
+        <v>994.7399262092307</v>
       </c>
       <c r="V35" t="n">
-        <v>759.5368714952685</v>
+        <v>759.5368714952672</v>
       </c>
       <c r="W35" t="n">
-        <v>515.7252795953216</v>
+        <v>515.7252795953201</v>
       </c>
       <c r="X35" t="n">
-        <v>318.4709023623239</v>
+        <v>318.4709023623224</v>
       </c>
       <c r="Y35" t="n">
-        <v>202.9987481372669</v>
+        <v>202.9987481372655</v>
       </c>
     </row>
     <row r="36">
@@ -6983,76 +6983,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>381.3722089875799</v>
+        <v>513.0455124857424</v>
       </c>
       <c r="C36" t="n">
-        <v>381.3722089875799</v>
+        <v>148.298126177137</v>
       </c>
       <c r="D36" t="n">
-        <v>29.92000000000147</v>
+        <v>29.92</v>
       </c>
       <c r="E36" t="n">
-        <v>29.92000000000147</v>
+        <v>29.92</v>
       </c>
       <c r="F36" t="n">
-        <v>29.92000000000147</v>
+        <v>29.92</v>
       </c>
       <c r="G36" t="n">
-        <v>29.92000000000147</v>
+        <v>29.92</v>
       </c>
       <c r="H36" t="n">
-        <v>29.92000000000147</v>
+        <v>29.92</v>
       </c>
       <c r="I36" t="n">
-        <v>29.92000000000147</v>
+        <v>29.92</v>
       </c>
       <c r="J36" t="n">
-        <v>67.57895890369505</v>
+        <v>227.711345930016</v>
       </c>
       <c r="K36" t="n">
-        <v>90.04581399652528</v>
+        <v>250.1782010228462</v>
       </c>
       <c r="L36" t="n">
-        <v>460.3058139965739</v>
+        <v>620.4382010228733</v>
       </c>
       <c r="M36" t="n">
-        <v>744.4012057394332</v>
+        <v>904.5335927657325</v>
       </c>
       <c r="N36" t="n">
-        <v>1080.937204214926</v>
+        <v>1241.069591241225</v>
       </c>
       <c r="O36" t="n">
-        <v>1451.197204214975</v>
+        <v>1451.197204214901</v>
       </c>
       <c r="P36" t="n">
-        <v>1496.000000000073</v>
+        <v>1496</v>
       </c>
       <c r="Q36" t="n">
-        <v>1422.956031069343</v>
+        <v>1496</v>
       </c>
       <c r="R36" t="n">
-        <v>1320.671196754571</v>
+        <v>1393.715165685228</v>
       </c>
       <c r="S36" t="n">
-        <v>1265.215326769352</v>
+        <v>1338.259295700009</v>
       </c>
       <c r="T36" t="n">
-        <v>1259.987100039255</v>
+        <v>1333.031068969912</v>
       </c>
       <c r="U36" t="n">
-        <v>1256.796770950444</v>
+        <v>1329.840739881101</v>
       </c>
       <c r="V36" t="n">
-        <v>1239.109228332747</v>
+        <v>952.0629621032956</v>
       </c>
       <c r="W36" t="n">
-        <v>1203.378780949082</v>
+        <v>916.3325147196305</v>
       </c>
       <c r="X36" t="n">
-        <v>1136.927764543235</v>
+        <v>893.2388385121683</v>
       </c>
       <c r="Y36" t="n">
-        <v>759.1499867654074</v>
+        <v>890.8232902635477</v>
       </c>
     </row>
     <row r="37">
@@ -7062,76 +7062,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>29.92000000000147</v>
+        <v>225.65957815255</v>
       </c>
       <c r="C37" t="n">
-        <v>152.9520058184372</v>
+        <v>225.65957815255</v>
       </c>
       <c r="D37" t="n">
-        <v>263.3011499434373</v>
+        <v>225.65957815255</v>
       </c>
       <c r="E37" t="n">
-        <v>263.3011499434373</v>
+        <v>340.518482363963</v>
       </c>
       <c r="F37" t="n">
-        <v>263.3011499434373</v>
+        <v>340.518482363963</v>
       </c>
       <c r="G37" t="n">
-        <v>263.3011499434373</v>
+        <v>340.518482363963</v>
       </c>
       <c r="H37" t="n">
-        <v>435.6729275618513</v>
+        <v>512.890259982377</v>
       </c>
       <c r="I37" t="n">
-        <v>673.5390137110491</v>
+        <v>512.890259982377</v>
       </c>
       <c r="J37" t="n">
-        <v>1043.799013711098</v>
+        <v>883.150259982404</v>
       </c>
       <c r="K37" t="n">
-        <v>1043.799013711098</v>
+        <v>1066.665307034026</v>
       </c>
       <c r="L37" t="n">
-        <v>1066.665307034028</v>
+        <v>1066.665307034026</v>
       </c>
       <c r="M37" t="n">
-        <v>1046.573449184127</v>
+        <v>1046.573449184125</v>
       </c>
       <c r="N37" t="n">
-        <v>972.925848727548</v>
+        <v>972.9258487275466</v>
       </c>
       <c r="O37" t="n">
-        <v>821.5090014213729</v>
+        <v>821.5090014213715</v>
       </c>
       <c r="P37" t="n">
-        <v>608.9778913530681</v>
+        <v>608.9778913530666</v>
       </c>
       <c r="Q37" t="n">
-        <v>332.7937838524641</v>
+        <v>332.7937838524626</v>
       </c>
       <c r="R37" t="n">
-        <v>29.92000000000147</v>
+        <v>29.92</v>
       </c>
       <c r="S37" t="n">
-        <v>29.92000000000147</v>
+        <v>29.92</v>
       </c>
       <c r="T37" t="n">
-        <v>29.92000000000147</v>
+        <v>217.8251070276573</v>
       </c>
       <c r="U37" t="n">
-        <v>29.92000000000147</v>
+        <v>217.8251070276573</v>
       </c>
       <c r="V37" t="n">
-        <v>29.92000000000147</v>
+        <v>217.8251070276573</v>
       </c>
       <c r="W37" t="n">
-        <v>29.92000000000147</v>
+        <v>225.65957815255</v>
       </c>
       <c r="X37" t="n">
-        <v>29.92000000000147</v>
+        <v>225.65957815255</v>
       </c>
       <c r="Y37" t="n">
-        <v>29.92000000000147</v>
+        <v>225.65957815255</v>
       </c>
     </row>
     <row r="38">
@@ -7141,76 +7141,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>117.1408562629493</v>
+        <v>113.806583727033</v>
       </c>
       <c r="C38" t="n">
-        <v>64.13623177507661</v>
+        <v>60.80195923916038</v>
       </c>
       <c r="D38" t="n">
-        <v>50.66233708835965</v>
+        <v>47.32806455244342</v>
       </c>
       <c r="E38" t="n">
-        <v>43.22467081879536</v>
+        <v>39.89039828287913</v>
       </c>
       <c r="F38" t="n">
-        <v>35.25534889151066</v>
+        <v>35.25534889150917</v>
       </c>
       <c r="G38" t="n">
-        <v>29.92000000000147</v>
+        <v>29.92</v>
       </c>
       <c r="H38" t="n">
-        <v>29.92000000000147</v>
+        <v>29.92</v>
       </c>
       <c r="I38" t="n">
-        <v>29.92000000000147</v>
+        <v>29.92</v>
       </c>
       <c r="J38" t="n">
-        <v>119.195984973141</v>
+        <v>119.1959849731395</v>
       </c>
       <c r="K38" t="n">
-        <v>489.455984973159</v>
+        <v>304.9927226113305</v>
       </c>
       <c r="L38" t="n">
-        <v>719.9532672847168</v>
+        <v>535.4900049228883</v>
       </c>
       <c r="M38" t="n">
-        <v>739.4315875548118</v>
+        <v>739.4315875547475</v>
       </c>
       <c r="N38" t="n">
-        <v>739.4315875548118</v>
+        <v>1109.691587554807</v>
       </c>
       <c r="O38" t="n">
-        <v>915.9847596412844</v>
+        <v>1286.24475964128</v>
       </c>
       <c r="P38" t="n">
-        <v>1125.740000000005</v>
+        <v>1496</v>
       </c>
       <c r="Q38" t="n">
-        <v>1496.000000000073</v>
+        <v>1496</v>
       </c>
       <c r="R38" t="n">
-        <v>1496.000000000073</v>
+        <v>1496</v>
       </c>
       <c r="S38" t="n">
-        <v>1431.123215102544</v>
+        <v>1431.123215102471</v>
       </c>
       <c r="T38" t="n">
-        <v>1246.055417711628</v>
+        <v>1246.055417711555</v>
       </c>
       <c r="U38" t="n">
-        <v>994.7399262092321</v>
+        <v>991.4056536733159</v>
       </c>
       <c r="V38" t="n">
-        <v>759.5368714952685</v>
+        <v>756.2025989593524</v>
       </c>
       <c r="W38" t="n">
-        <v>515.7252795953216</v>
+        <v>512.3910070594054</v>
       </c>
       <c r="X38" t="n">
-        <v>318.4709023623239</v>
+        <v>315.1366298264077</v>
       </c>
       <c r="Y38" t="n">
-        <v>202.9987481372669</v>
+        <v>199.6644756013507</v>
       </c>
     </row>
     <row r="39">
@@ -7220,76 +7220,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1070.572551977266</v>
+        <v>29.92</v>
       </c>
       <c r="C39" t="n">
-        <v>1070.572551977266</v>
+        <v>29.92</v>
       </c>
       <c r="D39" t="n">
-        <v>719.120342989688</v>
+        <v>29.92</v>
       </c>
       <c r="E39" t="n">
-        <v>372.9869114524024</v>
+        <v>29.92</v>
       </c>
       <c r="F39" t="n">
-        <v>29.92000000000147</v>
+        <v>29.92</v>
       </c>
       <c r="G39" t="n">
-        <v>29.92000000000147</v>
+        <v>29.92</v>
       </c>
       <c r="H39" t="n">
-        <v>29.92000000000147</v>
+        <v>29.92</v>
       </c>
       <c r="I39" t="n">
-        <v>29.92000000000147</v>
+        <v>29.92</v>
       </c>
       <c r="J39" t="n">
-        <v>67.57895890365543</v>
+        <v>67.57895890360007</v>
       </c>
       <c r="K39" t="n">
-        <v>90.04581399648566</v>
+        <v>90.0458139964303</v>
       </c>
       <c r="L39" t="n">
-        <v>460.3058139965541</v>
+        <v>460.3058139964898</v>
       </c>
       <c r="M39" t="n">
-        <v>744.4012057394134</v>
+        <v>744.4012057393491</v>
       </c>
       <c r="N39" t="n">
-        <v>1080.937204214906</v>
+        <v>1080.937204214842</v>
       </c>
       <c r="O39" t="n">
-        <v>1451.197204214975</v>
+        <v>1451.197204214901</v>
       </c>
       <c r="P39" t="n">
-        <v>1496.000000000073</v>
+        <v>1496</v>
       </c>
       <c r="Q39" t="n">
-        <v>1496.000000000073</v>
+        <v>1422.95603106927</v>
       </c>
       <c r="R39" t="n">
-        <v>1393.715165685301</v>
+        <v>1320.671196754497</v>
       </c>
       <c r="S39" t="n">
-        <v>1338.259295700083</v>
+        <v>1265.215326769279</v>
       </c>
       <c r="T39" t="n">
-        <v>1333.031068969985</v>
+        <v>1259.987100039182</v>
       </c>
       <c r="U39" t="n">
-        <v>1329.840739881174</v>
+        <v>1256.796770950371</v>
       </c>
       <c r="V39" t="n">
-        <v>1312.153197263477</v>
+        <v>879.0189931725324</v>
       </c>
       <c r="W39" t="n">
-        <v>1276.422749879812</v>
+        <v>501.2412153946939</v>
       </c>
       <c r="X39" t="n">
-        <v>1072.988100225887</v>
+        <v>123.4634376168555</v>
       </c>
       <c r="Y39" t="n">
-        <v>1070.572551977266</v>
+        <v>29.92</v>
       </c>
     </row>
     <row r="40">
@@ -7299,76 +7299,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>821.8788195528947</v>
+        <v>262.1654139983439</v>
       </c>
       <c r="C40" t="n">
-        <v>944.9108253713305</v>
+        <v>385.1974198167796</v>
       </c>
       <c r="D40" t="n">
-        <v>1055.259969496331</v>
+        <v>495.5465639417797</v>
       </c>
       <c r="E40" t="n">
-        <v>1055.259969496331</v>
+        <v>610.4054681531927</v>
       </c>
       <c r="F40" t="n">
-        <v>1055.259969496331</v>
+        <v>731.7964407451282</v>
       </c>
       <c r="G40" t="n">
-        <v>1055.259969496331</v>
+        <v>882.888191877915</v>
       </c>
       <c r="H40" t="n">
-        <v>1055.259969496331</v>
+        <v>1055.259969496329</v>
       </c>
       <c r="I40" t="n">
-        <v>1055.259969496331</v>
+        <v>1055.259969496329</v>
       </c>
       <c r="J40" t="n">
-        <v>1066.665307034028</v>
+        <v>1066.665307034026</v>
       </c>
       <c r="K40" t="n">
-        <v>1066.665307034028</v>
+        <v>1066.665307034026</v>
       </c>
       <c r="L40" t="n">
-        <v>1066.665307034028</v>
+        <v>1066.665307034026</v>
       </c>
       <c r="M40" t="n">
-        <v>1046.573449184127</v>
+        <v>1046.573449184125</v>
       </c>
       <c r="N40" t="n">
-        <v>972.925848727548</v>
+        <v>972.9258487275464</v>
       </c>
       <c r="O40" t="n">
-        <v>821.5090014213729</v>
+        <v>821.5090014213713</v>
       </c>
       <c r="P40" t="n">
-        <v>608.9778913530681</v>
+        <v>608.9778913530665</v>
       </c>
       <c r="Q40" t="n">
-        <v>332.7937838524641</v>
+        <v>332.7937838524626</v>
       </c>
       <c r="R40" t="n">
-        <v>29.92000000000147</v>
+        <v>29.92</v>
       </c>
       <c r="S40" t="n">
-        <v>29.92000000000147</v>
+        <v>29.92</v>
       </c>
       <c r="T40" t="n">
-        <v>44.05354190836351</v>
+        <v>29.92</v>
       </c>
       <c r="U40" t="n">
-        <v>287.6704719236993</v>
+        <v>29.92</v>
       </c>
       <c r="V40" t="n">
-        <v>287.6704719236993</v>
+        <v>153.3780763320517</v>
       </c>
       <c r="W40" t="n">
-        <v>456.5913901833767</v>
+        <v>153.3780763320517</v>
       </c>
       <c r="X40" t="n">
-        <v>604.6521812075703</v>
+        <v>153.3780763320517</v>
       </c>
       <c r="Y40" t="n">
-        <v>713.0914818866025</v>
+        <v>153.3780763320517</v>
       </c>
     </row>
     <row r="41">
@@ -7378,76 +7378,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>187.9751295383792</v>
+        <v>554.9413847628364</v>
       </c>
       <c r="C41" t="n">
-        <v>29.92000000000147</v>
+        <v>396.8862552244586</v>
       </c>
       <c r="D41" t="n">
-        <v>29.92000000000147</v>
+        <v>278.3618554872367</v>
       </c>
       <c r="E41" t="n">
-        <v>29.92000000000147</v>
+        <v>253.325680919804</v>
       </c>
       <c r="F41" t="n">
-        <v>29.92000000000147</v>
+        <v>140.3058539420142</v>
       </c>
       <c r="G41" t="n">
-        <v>29.92000000000147</v>
+        <v>29.92</v>
       </c>
       <c r="H41" t="n">
-        <v>29.92000000000147</v>
+        <v>29.92</v>
       </c>
       <c r="I41" t="n">
-        <v>29.92000000000147</v>
+        <v>29.92</v>
       </c>
       <c r="J41" t="n">
-        <v>119.195984973141</v>
+        <v>119.1959849731395</v>
       </c>
       <c r="K41" t="n">
-        <v>304.9927226113319</v>
+        <v>304.9927226113305</v>
       </c>
       <c r="L41" t="n">
-        <v>535.4900049228896</v>
+        <v>535.4900049228883</v>
       </c>
       <c r="M41" t="n">
-        <v>905.750004923005</v>
+        <v>545.7247596411139</v>
       </c>
       <c r="N41" t="n">
-        <v>1109.69158755488</v>
+        <v>915.9847596411968</v>
       </c>
       <c r="O41" t="n">
-        <v>1286.244759641353</v>
+        <v>1286.24475964128</v>
       </c>
       <c r="P41" t="n">
-        <v>1496.000000000073</v>
+        <v>1496</v>
       </c>
       <c r="Q41" t="n">
-        <v>1496.000000000073</v>
+        <v>1496</v>
       </c>
       <c r="R41" t="n">
-        <v>1496.000000000073</v>
+        <v>1496</v>
       </c>
       <c r="S41" t="n">
-        <v>1370.304065461625</v>
+        <v>1326.072710051965</v>
       </c>
       <c r="T41" t="n">
-        <v>1370.304065461625</v>
+        <v>1326.072710051965</v>
       </c>
       <c r="U41" t="n">
-        <v>1370.304065461625</v>
+        <v>966.3724409632212</v>
       </c>
       <c r="V41" t="n">
-        <v>1030.050505697157</v>
+        <v>966.3724409632212</v>
       </c>
       <c r="W41" t="n">
-        <v>681.1884087467047</v>
+        <v>966.3724409632212</v>
       </c>
       <c r="X41" t="n">
-        <v>378.8835264632019</v>
+        <v>966.3724409632212</v>
       </c>
       <c r="Y41" t="n">
-        <v>378.8835264632019</v>
+        <v>745.8497816876592</v>
       </c>
     </row>
     <row r="42">
@@ -7457,76 +7457,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>318.0281146698638</v>
+        <v>315.6172324016843</v>
       </c>
       <c r="C42" t="n">
-        <v>249.2403243208544</v>
+        <v>246.8294420526749</v>
       </c>
       <c r="D42" t="n">
-        <v>193.7477112928719</v>
+        <v>191.3368290246924</v>
       </c>
       <c r="E42" t="n">
-        <v>143.5738757151824</v>
+        <v>141.1629934470029</v>
       </c>
       <c r="F42" t="n">
-        <v>96.46656022237748</v>
+        <v>94.05567795419802</v>
       </c>
       <c r="G42" t="n">
-        <v>64.1936918904459</v>
+        <v>61.78280962226643</v>
       </c>
       <c r="H42" t="n">
-        <v>32.33088226817947</v>
+        <v>29.92</v>
       </c>
       <c r="I42" t="n">
-        <v>29.92000000000147</v>
+        <v>29.92</v>
       </c>
       <c r="J42" t="n">
-        <v>174.7530143484447</v>
+        <v>67.57895890355329</v>
       </c>
       <c r="K42" t="n">
-        <v>197.219869441275</v>
+        <v>90.04581399638352</v>
       </c>
       <c r="L42" t="n">
-        <v>567.4798694413903</v>
+        <v>460.3058139964664</v>
       </c>
       <c r="M42" t="n">
-        <v>851.5752611842495</v>
+        <v>744.4012057393256</v>
       </c>
       <c r="N42" t="n">
-        <v>1188.111259659742</v>
+        <v>1080.937204214818</v>
       </c>
       <c r="O42" t="n">
-        <v>1234.237999492831</v>
+        <v>1451.197204214901</v>
       </c>
       <c r="P42" t="n">
-        <v>1496.000000000073</v>
+        <v>1496</v>
       </c>
       <c r="Q42" t="n">
-        <v>1496.000000000073</v>
+        <v>1496</v>
       </c>
       <c r="R42" t="n">
-        <v>1288.664660634796</v>
+        <v>1286.253778366616</v>
       </c>
       <c r="S42" t="n">
-        <v>1128.158285599073</v>
+        <v>1125.747403330893</v>
       </c>
       <c r="T42" t="n">
-        <v>1017.87955381847</v>
+        <v>1015.46867155029</v>
       </c>
       <c r="U42" t="n">
-        <v>909.638719679154</v>
+        <v>907.2278374109744</v>
       </c>
       <c r="V42" t="n">
-        <v>786.9006720109518</v>
+        <v>784.4897897427722</v>
       </c>
       <c r="W42" t="n">
-        <v>646.1197195767816</v>
+        <v>643.708837308602</v>
       </c>
       <c r="X42" t="n">
-        <v>517.9755383188143</v>
+        <v>515.5646560506348</v>
       </c>
       <c r="Y42" t="n">
-        <v>410.5094850196887</v>
+        <v>408.0986027515092</v>
       </c>
     </row>
     <row r="43">
@@ -7536,76 +7536,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>470.7817775581359</v>
+        <v>470.7817775581344</v>
       </c>
       <c r="C43" t="n">
-        <v>490.8537833765717</v>
+        <v>490.8537833765702</v>
       </c>
       <c r="D43" t="n">
-        <v>498.2429275015718</v>
+        <v>498.2429275015703</v>
       </c>
       <c r="E43" t="n">
-        <v>510.1418317129848</v>
+        <v>510.1418317129833</v>
       </c>
       <c r="F43" t="n">
-        <v>528.5728043049203</v>
+        <v>528.5728043049188</v>
       </c>
       <c r="G43" t="n">
-        <v>576.7045554377072</v>
+        <v>576.7045554377057</v>
       </c>
       <c r="H43" t="n">
-        <v>646.1163330561212</v>
+        <v>646.1163330561196</v>
       </c>
       <c r="I43" t="n">
-        <v>781.0224192053189</v>
+        <v>781.0224192053173</v>
       </c>
       <c r="J43" t="n">
-        <v>1082.497756743016</v>
+        <v>1082.497756743015</v>
       </c>
       <c r="K43" t="n">
-        <v>1163.052803794639</v>
+        <v>1163.052803794637</v>
       </c>
       <c r="L43" t="n">
-        <v>1130.572470666231</v>
+        <v>1163.052803794637</v>
       </c>
       <c r="M43" t="n">
-        <v>1130.572470666231</v>
+        <v>1163.052803794637</v>
       </c>
       <c r="N43" t="n">
-        <v>951.8743651591475</v>
+        <v>984.3546982875537</v>
       </c>
       <c r="O43" t="n">
-        <v>695.4070128024673</v>
+        <v>727.8873459308736</v>
       </c>
       <c r="P43" t="n">
-        <v>695.4070128024673</v>
+        <v>410.3057308120637</v>
       </c>
       <c r="Q43" t="n">
-        <v>317.6292350241584</v>
+        <v>32.52795303420135</v>
       </c>
       <c r="R43" t="n">
-        <v>88.34429643772594</v>
+        <v>29.92</v>
       </c>
       <c r="S43" t="n">
-        <v>29.92000000000147</v>
+        <v>29.92</v>
       </c>
       <c r="T43" t="n">
-        <v>114.8651070276588</v>
+        <v>114.8651070276573</v>
       </c>
       <c r="U43" t="n">
-        <v>255.5220370429946</v>
+        <v>255.5220370429931</v>
       </c>
       <c r="V43" t="n">
-        <v>348.4134299289406</v>
+        <v>348.4134299289391</v>
       </c>
       <c r="W43" t="n">
-        <v>414.374348188618</v>
+        <v>414.3743481886165</v>
       </c>
       <c r="X43" t="n">
-        <v>459.4751392128115</v>
+        <v>459.4751392128101</v>
       </c>
       <c r="Y43" t="n">
-        <v>464.9544398918438</v>
+        <v>464.9544398918423</v>
       </c>
     </row>
     <row r="44">
@@ -7615,76 +7615,76 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>612.336771568077</v>
+        <v>144.8791919128322</v>
       </c>
       <c r="C44" t="n">
-        <v>454.2816420296992</v>
+        <v>29.92</v>
       </c>
       <c r="D44" t="n">
-        <v>335.7572422924773</v>
+        <v>29.92</v>
       </c>
       <c r="E44" t="n">
-        <v>223.2690709724079</v>
+        <v>29.92</v>
       </c>
       <c r="F44" t="n">
-        <v>110.2492439946182</v>
+        <v>29.92</v>
       </c>
       <c r="G44" t="n">
-        <v>110.2492439946182</v>
+        <v>29.92</v>
       </c>
       <c r="H44" t="n">
-        <v>29.91999999999998</v>
+        <v>29.92</v>
       </c>
       <c r="I44" t="n">
-        <v>29.91999999999998</v>
+        <v>29.92</v>
       </c>
       <c r="J44" t="n">
-        <v>400.1800000001873</v>
+        <v>119.1959849731395</v>
       </c>
       <c r="K44" t="n">
-        <v>585.9767376383783</v>
+        <v>304.9927226113305</v>
       </c>
       <c r="L44" t="n">
-        <v>816.4740199499361</v>
+        <v>535.4900049228883</v>
       </c>
       <c r="M44" t="n">
-        <v>816.4740199499361</v>
+        <v>905.7500049230684</v>
       </c>
       <c r="N44" t="n">
-        <v>1109.691587554806</v>
+        <v>905.7500049230684</v>
       </c>
       <c r="O44" t="n">
-        <v>1286.244759641279</v>
+        <v>1082.303177009541</v>
       </c>
       <c r="P44" t="n">
-        <v>1495.999999999999</v>
+        <v>1292.058417368261</v>
       </c>
       <c r="Q44" t="n">
-        <v>1495.999999999999</v>
+        <v>1496</v>
       </c>
       <c r="R44" t="n">
-        <v>1495.999999999999</v>
+        <v>1496</v>
       </c>
       <c r="S44" t="n">
-        <v>1326.072710051965</v>
+        <v>1496</v>
       </c>
       <c r="T44" t="n">
-        <v>1326.072710051965</v>
+        <v>1496</v>
       </c>
       <c r="U44" t="n">
-        <v>1326.072710051965</v>
+        <v>1136.299730911256</v>
       </c>
       <c r="V44" t="n">
-        <v>1326.072710051965</v>
+        <v>796.0461711467871</v>
       </c>
       <c r="W44" t="n">
-        <v>1326.072710051965</v>
+        <v>447.184074196335</v>
       </c>
       <c r="X44" t="n">
-        <v>1023.767827768462</v>
+        <v>144.8791919128322</v>
       </c>
       <c r="Y44" t="n">
-        <v>803.2451684928998</v>
+        <v>144.8791919128322</v>
       </c>
     </row>
     <row r="45">
@@ -7694,76 +7694,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>315.6172324016843</v>
+        <v>318.0281146697906</v>
       </c>
       <c r="C45" t="n">
-        <v>246.8294420526749</v>
+        <v>249.2403243207812</v>
       </c>
       <c r="D45" t="n">
-        <v>191.3368290246924</v>
+        <v>193.7477112927987</v>
       </c>
       <c r="E45" t="n">
-        <v>141.1629934470029</v>
+        <v>143.5738757151092</v>
       </c>
       <c r="F45" t="n">
-        <v>94.05567795419799</v>
+        <v>96.46656022230427</v>
       </c>
       <c r="G45" t="n">
-        <v>61.78280962226641</v>
+        <v>64.19369189037269</v>
       </c>
       <c r="H45" t="n">
-        <v>29.91999999999998</v>
+        <v>32.33088226810625</v>
       </c>
       <c r="I45" t="n">
-        <v>29.91999999999998</v>
+        <v>29.92</v>
       </c>
       <c r="J45" t="n">
-        <v>98.79078061605924</v>
+        <v>164.0523427568667</v>
       </c>
       <c r="K45" t="n">
-        <v>414.1790741632728</v>
+        <v>186.519197849697</v>
       </c>
       <c r="L45" t="n">
-        <v>784.4390741634602</v>
+        <v>243.3466092742253</v>
       </c>
       <c r="M45" t="n">
-        <v>1068.534465906319</v>
+        <v>527.4420010170845</v>
       </c>
       <c r="N45" t="n">
-        <v>1405.070464381812</v>
+        <v>863.9779994925773</v>
       </c>
       <c r="O45" t="n">
-        <v>1451.1972042149</v>
+        <v>1234.237999492757</v>
       </c>
       <c r="P45" t="n">
-        <v>1495.999999999999</v>
+        <v>1496</v>
       </c>
       <c r="Q45" t="n">
-        <v>1493.589117731894</v>
+        <v>1496</v>
       </c>
       <c r="R45" t="n">
-        <v>1286.253778366616</v>
+        <v>1288.664660634723</v>
       </c>
       <c r="S45" t="n">
-        <v>1125.747403330893</v>
+        <v>1128.158285598999</v>
       </c>
       <c r="T45" t="n">
-        <v>1015.46867155029</v>
+        <v>1017.879553818397</v>
       </c>
       <c r="U45" t="n">
-        <v>907.2278374109744</v>
+        <v>909.6387196790807</v>
       </c>
       <c r="V45" t="n">
-        <v>784.4897897427722</v>
+        <v>786.9006720108786</v>
       </c>
       <c r="W45" t="n">
-        <v>643.708837308602</v>
+        <v>646.1197195767083</v>
       </c>
       <c r="X45" t="n">
-        <v>515.5646560506348</v>
+        <v>517.9755383187411</v>
       </c>
       <c r="Y45" t="n">
-        <v>408.0986027515092</v>
+        <v>410.5094850196155</v>
       </c>
     </row>
     <row r="46">
@@ -7806,25 +7806,25 @@
         <v>1163.052803794637</v>
       </c>
       <c r="M46" t="n">
-        <v>1163.052803794637</v>
+        <v>1160.444850760535</v>
       </c>
       <c r="N46" t="n">
-        <v>984.3546982875537</v>
+        <v>981.7467452534515</v>
       </c>
       <c r="O46" t="n">
-        <v>727.8873459308736</v>
+        <v>725.2793928967715</v>
       </c>
       <c r="P46" t="n">
-        <v>410.3057308120637</v>
+        <v>407.6977777779616</v>
       </c>
       <c r="Q46" t="n">
-        <v>32.52795303409476</v>
+        <v>29.92</v>
       </c>
       <c r="R46" t="n">
-        <v>29.91999999999998</v>
+        <v>29.92</v>
       </c>
       <c r="S46" t="n">
-        <v>29.91999999999998</v>
+        <v>29.92</v>
       </c>
       <c r="T46" t="n">
         <v>114.8651070276573</v>
@@ -7964,7 +7964,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>374.2405037325275</v>
+        <v>0.2405037325275146</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -7973,19 +7973,19 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>846.2608914614127</v>
+        <v>655.6021670241489</v>
       </c>
       <c r="N2" t="n">
         <v>778.0826666125488</v>
       </c>
       <c r="O2" t="n">
-        <v>1.159015302735668</v>
+        <v>375.1590153027356</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>311.8831458198699</v>
+        <v>502.5418702571336</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8204,7 +8204,7 @@
         <v>0.2405037325275146</v>
       </c>
       <c r="K5" t="n">
-        <v>183.3412755627362</v>
+        <v>321.8400703517588</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -8213,7 +8213,7 @@
         <v>846.2608914614127</v>
       </c>
       <c r="N5" t="n">
-        <v>778.0826666125488</v>
+        <v>639.5838718235262</v>
       </c>
       <c r="O5" t="n">
         <v>1.159015302735668</v>
@@ -8438,19 +8438,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>374.2405037325275</v>
+        <v>0.2405037325275146</v>
       </c>
       <c r="K8" t="n">
         <v>321.8400703517588</v>
       </c>
       <c r="L8" t="n">
-        <v>309.2909949748744</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>772.4711016975157</v>
+        <v>846.2608914614127</v>
       </c>
       <c r="N8" t="n">
-        <v>404.0826666125488</v>
+        <v>778.0826666125488</v>
       </c>
       <c r="O8" t="n">
         <v>1.159015302735668</v>
@@ -8459,7 +8459,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>128.5418702571336</v>
+        <v>364.0430754681111</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8681,13 +8681,13 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>422.1744623115578</v>
       </c>
       <c r="M11" t="n">
-        <v>892.5421829639411</v>
+        <v>940.1988562855333</v>
       </c>
       <c r="N11" t="n">
-        <v>868.993772140187</v>
+        <v>399.1626365070371</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -8912,19 +8912,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>467.3265276381908</v>
+        <v>467.326527638191</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>422.1744623115576</v>
       </c>
       <c r="M14" t="n">
-        <v>477.8621608560239</v>
+        <v>940.1988562855333</v>
       </c>
       <c r="N14" t="n">
-        <v>213.993772140187</v>
+        <v>213.9937721401869</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -8933,7 +8933,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>615.8520732695737</v>
+        <v>161.6456521146628</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9149,19 +9149,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>467.3265276381908</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>422.1744623115578</v>
+        <v>422.1744623115577</v>
       </c>
       <c r="M17" t="n">
-        <v>658.0411930141927</v>
+        <v>900.6724572385396</v>
       </c>
       <c r="N17" t="n">
-        <v>213.993772140187</v>
+        <v>868.9937721401869</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -9389,16 +9389,16 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
-        <v>467.3265276382094</v>
+        <v>467.3265276381908</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>477.8621608560788</v>
+        <v>425.2156553257504</v>
       </c>
       <c r="N20" t="n">
-        <v>213.993772140187</v>
+        <v>868.993772140187</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -9407,7 +9407,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>615.8520732695737</v>
+        <v>13.49857879984722</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9626,16 +9626,16 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>467.3265276381908</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>290.1886884942807</v>
+        <v>425.2156553257495</v>
       </c>
       <c r="N23" t="n">
-        <v>868.9937721401948</v>
+        <v>868.9937721401866</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -9644,7 +9644,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>615.8520732695737</v>
+        <v>13.49857879984722</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9860,7 +9860,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -9869,16 +9869,16 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>290.1886884942763</v>
+        <v>940.1988562855339</v>
       </c>
       <c r="N26" t="n">
-        <v>868.993772140198</v>
+        <v>213.9937721401856</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>435.294568794836</v>
       </c>
       <c r="Q26" t="n">
         <v>615.8520732695737</v>
@@ -10100,16 +10100,16 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>467.3265276382093</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>422.174462311576</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>433.3459296003637</v>
+        <v>720.4934250803628</v>
       </c>
       <c r="N29" t="n">
-        <v>868.9937721402039</v>
+        <v>868.99377214019</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -10118,7 +10118,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>13.49857879984722</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10340,22 +10340,22 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>422.1744623115577</v>
       </c>
       <c r="M32" t="n">
-        <v>846.1834570112026</v>
+        <v>940.1988562855407</v>
       </c>
       <c r="N32" t="n">
-        <v>868.9937721402125</v>
+        <v>227.1138786234524</v>
       </c>
       <c r="O32" t="n">
-        <v>476.6634625389421</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>13.49857879984722</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10574,16 +10574,16 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>186.3265276382093</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>304.8739272654473</v>
+        <v>491.2004549036002</v>
       </c>
       <c r="N35" t="n">
-        <v>587.9937721402362</v>
+        <v>587.9937721402089</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -10650,13 +10650,13 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J36" t="n">
-        <v>65.71485604261431</v>
+        <v>227.4647419277884</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>316.5985743187074</v>
+        <v>316.5985743186856</v>
       </c>
       <c r="M36" t="n">
         <v>471.6948204301074</v>
@@ -10665,7 +10665,7 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O36" t="n">
-        <v>327.4073335019801</v>
+        <v>165.6574476167553</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
@@ -10811,16 +10811,16 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>186.3265276382093</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>304.8739272654273</v>
+        <v>491.2004549035647</v>
       </c>
       <c r="N38" t="n">
-        <v>213.993772140187</v>
+        <v>587.9937721402389</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -10829,7 +10829,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>387.4985787999165</v>
+        <v>13.49857879984722</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -10887,13 +10887,13 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J39" t="n">
-        <v>65.7148560425743</v>
+        <v>65.71485604251987</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>316.5985743187275</v>
+        <v>316.5985743187184</v>
       </c>
       <c r="M39" t="n">
         <v>471.6948204301074</v>
@@ -10902,7 +10902,7 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O39" t="n">
-        <v>327.4073335020001</v>
+        <v>327.407333501991</v>
       </c>
       <c r="P39" t="n">
         <v>0</v>
@@ -11054,13 +11054,13 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>659.19885628565</v>
+        <v>295.5369923645399</v>
       </c>
       <c r="N41" t="n">
-        <v>419.9953707582428</v>
+        <v>587.9937721402616</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>195.6634625390003</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
@@ -11124,13 +11124,13 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J42" t="n">
-        <v>173.9714777039777</v>
+        <v>65.7148560424726</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>316.5985743187748</v>
+        <v>316.598574318742</v>
       </c>
       <c r="M42" t="n">
         <v>471.6948204301074</v>
@@ -11139,10 +11139,10 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>327.4073335020147</v>
       </c>
       <c r="P42" t="n">
-        <v>219.1507118405495</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
         <v>17.27519534353338</v>
@@ -11282,7 +11282,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>283.8222374010584</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -11291,10 +11291,10 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>285.1988562855334</v>
+        <v>659.198856285697</v>
       </c>
       <c r="N44" t="n">
-        <v>510.1731333572275</v>
+        <v>213.9937721401687</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -11303,7 +11303,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>13.49857879984722</v>
+        <v>219.500177417765</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -11361,13 +11361,13 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J45" t="n">
-        <v>97.24194868136752</v>
+        <v>163.162718520567</v>
       </c>
       <c r="K45" t="n">
-        <v>295.8802408630135</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>316.5985743188475</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
         <v>471.6948204301074</v>
@@ -11376,10 +11376,10 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>327.4073335021129</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>219.1507118405495</v>
       </c>
       <c r="Q45" t="n">
         <v>17.27519534353338</v>
@@ -23226,7 +23226,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>0.6960849964949034</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -23238,7 +23238,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6960849964948983</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -23423,10 +23423,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.850361477466265</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.850361477466379</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -23475,7 +23475,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6960849964948983</v>
+        <v>0.696084996494875</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -23648,7 +23648,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.850361477466352</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -23669,7 +23669,7 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.85036147746635</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -23706,13 +23706,13 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>0.6960849964949034</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6960849964948983</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -23943,7 +23943,7 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6960849964230533</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -23985,7 +23985,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>0.696084996495216</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -24143,7 +24143,7 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.85036147746602</v>
+        <v>2.850361477466322</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -24186,7 +24186,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.6960849964229539</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -24222,7 +24222,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>0.6960849964951876</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
@@ -24365,7 +24365,7 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.850361477466578</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -24380,7 +24380,7 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.850361477466439</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -24423,7 +24423,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.6960849964238349</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -24468,7 +24468,7 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>0.696084996472905</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
@@ -24660,7 +24660,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.6960849964283915</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -24702,7 +24702,7 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>0.6960849964951308</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -24833,7 +24833,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>2.850361477466112</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -24854,7 +24854,7 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.850361477466322</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -24900,7 +24900,7 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>0.696084996422428</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -24936,7 +24936,7 @@
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>0.6960849964238491</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
@@ -25070,7 +25070,7 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.850361477466563</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -25085,7 +25085,7 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.850361477466038</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -25170,10 +25170,10 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>3.30092981048444</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>3.300929810555601</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
@@ -25368,7 +25368,7 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>3.300929810555594</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -25413,7 +25413,7 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>3.300929810484433</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -25599,19 +25599,19 @@
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>117.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>111.3632896068686</v>
+        <v>86.57747678511029</v>
       </c>
       <c r="F41" t="n">
-        <v>111.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>109.2819954025941</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>99.89995518593948</v>
+        <v>99.89995518593946</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -25644,25 +25644,25 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>43.78904185549054</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
         <v>287.2171194170061</v>
       </c>
       <c r="U41" t="n">
-        <v>356.1032663978569</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>336.8510241668239</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>345.3734759809475</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>299.2818334606677</v>
       </c>
       <c r="Y41" t="n">
-        <v>218.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -25781,7 +25781,7 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>32.15552979712345</v>
       </c>
       <c r="M43" t="n">
         <v>123.8909392714024</v>
@@ -25793,16 +25793,16 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>314.4057989676218</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.422266425072166</v>
+        <v>3.422266425514181</v>
       </c>
       <c r="R43" t="n">
-        <v>176.8529568133698</v>
+        <v>401.2631725100786</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>57.84005347334727</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -25830,25 +25830,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>188.9993129555745</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>42.66497824929004</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>117.3391557398498</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>111.3632896068686</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>111.8896287080119</v>
       </c>
       <c r="G44" t="n">
         <v>109.2819954025941</v>
       </c>
       <c r="H44" t="n">
-        <v>20.37400363126747</v>
+        <v>99.89995518593948</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -25881,25 +25881,25 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>168.2280170485541</v>
       </c>
       <c r="T44" t="n">
         <v>287.2171194170061</v>
       </c>
       <c r="U44" t="n">
-        <v>356.1032663978569</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>336.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>345.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>218.3174326828064</v>
       </c>
     </row>
     <row r="45">
@@ -26018,10 +26018,10 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>32.15552979712345</v>
+        <v>32.15552979712344</v>
       </c>
       <c r="M46" t="n">
-        <v>123.8909392714024</v>
+        <v>121.3090657676412</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
@@ -26033,13 +26033,13 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.422266425408679</v>
+        <v>3.422266425415984</v>
       </c>
       <c r="R46" t="n">
-        <v>401.2631725101841</v>
+        <v>403.845046013938</v>
       </c>
       <c r="S46" t="n">
-        <v>57.84005347334727</v>
+        <v>57.84005347334724</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7808824.686420081</v>
+        <v>7808824.686420074</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8910671.256800069</v>
+        <v>8910671.256800057</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10012517.82718006</v>
+        <v>10012517.82718004</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>11114364.39756005</v>
+        <v>11114364.39756003</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>12216210.96794004</v>
+        <v>12216210.96794002</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>13281144.86493412</v>
+        <v>13281144.8649341</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14382869.86546385</v>
+        <v>14382869.86546382</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15370480.02292385</v>
+        <v>15370480.02292382</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>16358090.18038385</v>
+        <v>16358090.18038382</v>
       </c>
     </row>
   </sheetData>
@@ -26269,7 +26269,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1101954.910291021</v>
+        <v>1101954.91029102</v>
       </c>
       <c r="C2" t="n">
         <v>1101954.910291021</v>
@@ -26281,37 +26281,37 @@
         <v>1101846.570379988</v>
       </c>
       <c r="F2" t="n">
-        <v>1101846.570379989</v>
+        <v>1101846.570379988</v>
       </c>
       <c r="G2" t="n">
         <v>1101846.570379988</v>
       </c>
       <c r="H2" t="n">
-        <v>1101846.570379993</v>
+        <v>1101846.570379988</v>
       </c>
       <c r="I2" t="n">
-        <v>1101846.570379993</v>
+        <v>1101846.570379988</v>
       </c>
       <c r="J2" t="n">
-        <v>1101846.570379993</v>
+        <v>1101846.570379989</v>
       </c>
       <c r="K2" t="n">
-        <v>1101846.570379992</v>
+        <v>1101846.570379988</v>
       </c>
       <c r="L2" t="n">
         <v>1101846.570379993</v>
       </c>
       <c r="M2" t="n">
-        <v>1101725.00052972</v>
+        <v>1101725.000529716</v>
       </c>
       <c r="N2" t="n">
-        <v>1101725.00052972</v>
+        <v>1101725.000529716</v>
       </c>
       <c r="O2" t="n">
-        <v>987610.1574599929</v>
+        <v>987610.1574599878</v>
       </c>
       <c r="P2" t="n">
-        <v>987610.1574599876</v>
+        <v>987610.1574599881</v>
       </c>
     </row>
     <row r="3">
@@ -26339,13 +26339,13 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>6.522896001115441e-09</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>386847.9999999999</v>
+        <v>386848</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>602419.1762101187</v>
+        <v>602219.8615549037</v>
       </c>
       <c r="C4" t="n">
-        <v>600410.2540226299</v>
+        <v>600210.9393674152</v>
       </c>
       <c r="D4" t="n">
-        <v>598398.6066068059</v>
+        <v>598199.291951591</v>
       </c>
       <c r="E4" t="n">
-        <v>508463.6174685807</v>
+        <v>508269.4590428486</v>
       </c>
       <c r="F4" t="n">
-        <v>506794.9519687437</v>
+        <v>506600.7935430115</v>
       </c>
       <c r="G4" t="n">
-        <v>505123.9837731232</v>
+        <v>504929.8253473911</v>
       </c>
       <c r="H4" t="n">
-        <v>503450.6963690012</v>
+        <v>503256.5379432672</v>
       </c>
       <c r="I4" t="n">
-        <v>501775.0730285023</v>
+        <v>501580.9146027683</v>
       </c>
       <c r="J4" t="n">
-        <v>500097.0968045235</v>
+        <v>499902.9383787904</v>
       </c>
       <c r="K4" t="n">
-        <v>498416.7505265516</v>
+        <v>498222.5921008176</v>
       </c>
       <c r="L4" t="n">
-        <v>496734.0167963771</v>
+        <v>496539.8583706462</v>
       </c>
       <c r="M4" t="n">
-        <v>522490.4615842159</v>
+        <v>522371.0444804639</v>
       </c>
       <c r="N4" t="n">
-        <v>520523.3308731506</v>
+        <v>520403.9137693986</v>
       </c>
       <c r="O4" t="n">
-        <v>447790.3844155943</v>
+        <v>447670.9673118423</v>
       </c>
       <c r="P4" t="n">
-        <v>446122.6297523478</v>
+        <v>446003.2126485964</v>
       </c>
     </row>
     <row r="5">
@@ -26443,31 +26443,31 @@
         <v>74642.611</v>
       </c>
       <c r="H5" t="n">
-        <v>74642.61100000114</v>
+        <v>74642.611</v>
       </c>
       <c r="I5" t="n">
-        <v>74642.61100000114</v>
+        <v>74642.611</v>
       </c>
       <c r="J5" t="n">
-        <v>74642.61100000111</v>
+        <v>74642.611</v>
       </c>
       <c r="K5" t="n">
-        <v>74642.61100000111</v>
+        <v>74642.611</v>
       </c>
       <c r="L5" t="n">
-        <v>74642.61100000111</v>
+        <v>74642.611</v>
       </c>
       <c r="M5" t="n">
-        <v>64115.19300000111</v>
+        <v>64115.193</v>
       </c>
       <c r="N5" t="n">
-        <v>64115.19300000111</v>
+        <v>64115.193</v>
       </c>
       <c r="O5" t="n">
-        <v>55372.01700000111</v>
+        <v>55372.01700000001</v>
       </c>
       <c r="P5" t="n">
-        <v>55372.01699999999</v>
+        <v>55372.01700000001</v>
       </c>
     </row>
     <row r="6">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>209847.3340809018</v>
+        <v>210046.6487361166</v>
       </c>
       <c r="C6" t="n">
-        <v>442954.256268391</v>
+        <v>443153.5709236056</v>
       </c>
       <c r="D6" t="n">
-        <v>444965.9036842143</v>
+        <v>445165.218339429</v>
       </c>
       <c r="E6" t="n">
-        <v>-93746.6580885929</v>
+        <v>-93552.49966286097</v>
       </c>
       <c r="F6" t="n">
-        <v>520409.0074112448</v>
+        <v>520603.165836976</v>
       </c>
       <c r="G6" t="n">
-        <v>522079.975606865</v>
+        <v>522274.1340325972</v>
       </c>
       <c r="H6" t="n">
-        <v>523753.2630109841</v>
+        <v>523947.4214367203</v>
       </c>
       <c r="I6" t="n">
-        <v>525428.8863514892</v>
+        <v>525623.0447772195</v>
       </c>
       <c r="J6" t="n">
-        <v>140258.8625754685</v>
+        <v>140453.0210011988</v>
       </c>
       <c r="K6" t="n">
-        <v>528787.2088534398</v>
+        <v>528981.3672791702</v>
       </c>
       <c r="L6" t="n">
-        <v>530469.9425836145</v>
+        <v>530664.1010093468</v>
       </c>
       <c r="M6" t="n">
-        <v>452719.3459455032</v>
+        <v>452838.7630492516</v>
       </c>
       <c r="N6" t="n">
-        <v>517086.4766565687</v>
+        <v>517205.8937603172</v>
       </c>
       <c r="O6" t="n">
-        <v>312447.7560443975</v>
+        <v>312567.1731481455</v>
       </c>
       <c r="P6" t="n">
-        <v>486115.5107076399</v>
+        <v>486234.9278113918</v>
       </c>
     </row>
   </sheetData>
@@ -26877,31 +26877,31 @@
         <v>655</v>
       </c>
       <c r="H4" t="n">
-        <v>655.0000000000185</v>
+        <v>655</v>
       </c>
       <c r="I4" t="n">
-        <v>655.0000000000185</v>
+        <v>655</v>
       </c>
       <c r="J4" t="n">
-        <v>655.0000000000183</v>
+        <v>655</v>
       </c>
       <c r="K4" t="n">
-        <v>655.0000000000183</v>
+        <v>655</v>
       </c>
       <c r="L4" t="n">
-        <v>655.0000000000183</v>
+        <v>655</v>
       </c>
       <c r="M4" t="n">
-        <v>374.0000000000183</v>
+        <v>374</v>
       </c>
       <c r="N4" t="n">
-        <v>374.0000000000183</v>
+        <v>374</v>
       </c>
       <c r="O4" t="n">
-        <v>374.0000000000183</v>
+        <v>374</v>
       </c>
       <c r="P4" t="n">
-        <v>373.9999999999998</v>
+        <v>374</v>
       </c>
     </row>
   </sheetData>
@@ -26984,16 +26984,16 @@
         <v>319</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>319</v>
@@ -27002,13 +27002,13 @@
         <v>-0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M2" t="n">
         <v>78</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O2" t="n">
         <v>215</v>
@@ -27094,7 +27094,7 @@
         <v>-0</v>
       </c>
       <c r="H4" t="n">
-        <v>1.142868182135069e-11</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>-0</v>
@@ -27335,7 +27335,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.853095454862341e-11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27436,7 +27436,7 @@
         <v>400</v>
       </c>
       <c r="C2" t="n">
-        <v>398.2013121321735</v>
+        <v>400</v>
       </c>
       <c r="D2" t="n">
         <v>400</v>
@@ -27454,7 +27454,7 @@
         <v>400</v>
       </c>
       <c r="I2" t="n">
-        <v>134.2726973711268</v>
+        <v>132.4740095033003</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27521,19 +27521,19 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>330.0491815260438</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>36.72043851444073</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27560,10 +27560,10 @@
         <v>145.073529241423</v>
       </c>
       <c r="R3" t="n">
-        <v>400</v>
+        <v>159.6519859716246</v>
       </c>
       <c r="S3" t="n">
-        <v>400</v>
+        <v>324.8092945090704</v>
       </c>
       <c r="T3" t="n">
         <v>400</v>
@@ -27591,13 +27591,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>310.7106609292461</v>
+        <v>400</v>
       </c>
       <c r="C4" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D4" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E4" t="n">
         <v>400</v>
@@ -27609,7 +27609,7 @@
         <v>244.8599384153005</v>
       </c>
       <c r="H4" t="n">
-        <v>400</v>
+        <v>347.6135343913642</v>
       </c>
       <c r="I4" t="n">
         <v>171.1020457840527</v>
@@ -27618,10 +27618,10 @@
         <v>22.26478490148153</v>
       </c>
       <c r="K4" t="n">
-        <v>267.1509377355693</v>
+        <v>400</v>
       </c>
       <c r="L4" t="n">
-        <v>396.2015953708939</v>
+        <v>400</v>
       </c>
       <c r="M4" t="n">
         <v>400</v>
@@ -27642,7 +27642,7 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>400</v>
+        <v>359.1680042930194</v>
       </c>
       <c r="T4" t="n">
         <v>209.2386648669134</v>
@@ -27651,10 +27651,10 @@
         <v>400</v>
       </c>
       <c r="V4" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W4" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X4" t="n">
         <v>400</v>
@@ -27752,16 +27752,16 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>325.5201396486123</v>
@@ -27794,22 +27794,22 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>145.073529241423</v>
+        <v>13.06671792211816</v>
       </c>
       <c r="R6" t="n">
-        <v>159.6519859716246</v>
+        <v>400</v>
       </c>
       <c r="S6" t="n">
-        <v>88.48881128536601</v>
+        <v>400</v>
       </c>
       <c r="T6" t="n">
-        <v>30.47344446279683</v>
+        <v>400</v>
       </c>
       <c r="U6" t="n">
         <v>400</v>
       </c>
       <c r="V6" t="n">
-        <v>140.7051052798087</v>
+        <v>400</v>
       </c>
       <c r="W6" t="n">
         <v>400</v>
@@ -27831,19 +27831,19 @@
         <v>400</v>
       </c>
       <c r="C7" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D7" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E7" t="n">
         <v>400</v>
       </c>
       <c r="F7" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G7" t="n">
-        <v>400</v>
+        <v>244.8599384153005</v>
       </c>
       <c r="H7" t="n">
         <v>400</v>
@@ -27852,7 +27852,7 @@
         <v>400</v>
       </c>
       <c r="J7" t="n">
-        <v>189.1651274515635</v>
+        <v>22.26478490148153</v>
       </c>
       <c r="K7" t="n">
         <v>400</v>
@@ -27879,13 +27879,13 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>359.1680042930194</v>
+        <v>400</v>
       </c>
       <c r="T7" t="n">
-        <v>209.2386648669134</v>
+        <v>400</v>
       </c>
       <c r="U7" t="n">
-        <v>150.9483584875727</v>
+        <v>277.8303950880375</v>
       </c>
       <c r="V7" t="n">
         <v>199.1703102162162</v>
@@ -27894,7 +27894,7 @@
         <v>226.3728098387097</v>
       </c>
       <c r="X7" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y7" t="n">
         <v>287.4653528494624</v>
@@ -27928,7 +27928,7 @@
         <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>132.4740095033003</v>
+        <v>134.2726973711268</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27955,7 +27955,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>225.120779732817</v>
+        <v>223.3220918649904</v>
       </c>
       <c r="S8" t="n">
         <v>400</v>
@@ -27986,10 +27986,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>384.5565566463266</v>
+        <v>10.55655664632661</v>
       </c>
       <c r="C9" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>347.9376868977026</v>
@@ -28007,7 +28007,7 @@
         <v>330.0491815260438</v>
       </c>
       <c r="I9" t="n">
-        <v>209.5726123064429</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -28031,7 +28031,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>53.82380753326782</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>400</v>
@@ -28040,22 +28040,22 @@
         <v>400</v>
       </c>
       <c r="T9" t="n">
+        <v>309.0654009929813</v>
+      </c>
+      <c r="U9" t="n">
         <v>400</v>
-      </c>
-      <c r="U9" t="n">
-        <v>26.1959257979226</v>
       </c>
       <c r="V9" t="n">
         <v>400</v>
       </c>
       <c r="W9" t="n">
-        <v>58.37314290982852</v>
+        <v>400</v>
       </c>
       <c r="X9" t="n">
         <v>400</v>
       </c>
       <c r="Y9" t="n">
-        <v>25.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="10">
@@ -28065,7 +28065,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C10" t="n">
         <v>400</v>
@@ -28077,10 +28077,10 @@
         <v>400</v>
       </c>
       <c r="F10" t="n">
-        <v>395.5545391634247</v>
+        <v>400</v>
       </c>
       <c r="G10" t="n">
-        <v>244.8599384153005</v>
+        <v>311.2238227277916</v>
       </c>
       <c r="H10" t="n">
         <v>227.1357818393235</v>
@@ -28119,16 +28119,16 @@
         <v>359.1680042930194</v>
       </c>
       <c r="T10" t="n">
-        <v>209.2386648669134</v>
+        <v>400</v>
       </c>
       <c r="U10" t="n">
         <v>400</v>
       </c>
       <c r="V10" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W10" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X10" t="n">
         <v>400</v>
@@ -28223,16 +28223,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>319</v>
+        <v>168.3712564811475</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="F12" t="n">
         <v>319</v>
@@ -28271,7 +28271,7 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>168.3712564811476</v>
+        <v>319</v>
       </c>
       <c r="S12" t="n">
         <v>319</v>
@@ -28460,28 +28460,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>319</v>
+        <v>96.05772723972439</v>
       </c>
       <c r="C15" t="n">
         <v>319</v>
       </c>
       <c r="D15" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>319</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>189.9476123064429</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -28517,19 +28517,19 @@
         <v>319</v>
       </c>
       <c r="U15" t="n">
-        <v>286.0053395461673</v>
+        <v>319</v>
       </c>
       <c r="V15" t="n">
         <v>319</v>
       </c>
       <c r="W15" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>319</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
     </row>
     <row r="16">
@@ -28697,10 +28697,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>319</v>
@@ -28745,7 +28745,7 @@
         <v>72.31352924142297</v>
       </c>
       <c r="R18" t="n">
-        <v>96.05772723972416</v>
+        <v>319</v>
       </c>
       <c r="S18" t="n">
         <v>319</v>
@@ -28754,7 +28754,7 @@
         <v>319</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="V18" t="n">
         <v>319</v>
@@ -28763,7 +28763,7 @@
         <v>319</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>96.05772723972456</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
@@ -28776,7 +28776,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>319.0000000000001</v>
+        <v>319</v>
       </c>
       <c r="C19" t="n">
         <v>319</v>
@@ -28934,19 +28934,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>319</v>
+        <v>96.05772723972427</v>
       </c>
       <c r="C21" t="n">
         <v>319</v>
       </c>
       <c r="D21" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
         <v>319</v>
@@ -28979,10 +28979,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>72.31352924142297</v>
       </c>
       <c r="R21" t="n">
-        <v>168.3712564811478</v>
+        <v>319</v>
       </c>
       <c r="S21" t="n">
         <v>319</v>
@@ -28991,13 +28991,13 @@
         <v>319</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="X21" t="n">
         <v>319</v>
@@ -29174,16 +29174,16 @@
         <v>319</v>
       </c>
       <c r="C24" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>319</v>
       </c>
       <c r="F24" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>319</v>
@@ -29216,7 +29216,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>72.31352924142297</v>
       </c>
       <c r="R24" t="n">
         <v>319</v>
@@ -29228,19 +29228,19 @@
         <v>319</v>
       </c>
       <c r="U24" t="n">
-        <v>168.3712564811474</v>
+        <v>319</v>
       </c>
       <c r="V24" t="n">
         <v>319</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>96.05772723972433</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
     </row>
     <row r="25">
@@ -29377,7 +29377,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>158.200955612214</v>
+        <v>158.2009556122366</v>
       </c>
       <c r="S26" t="n">
         <v>319</v>
@@ -29414,7 +29414,7 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="E27" t="n">
         <v>319</v>
@@ -29423,13 +29423,13 @@
         <v>319</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="H27" t="n">
         <v>319</v>
       </c>
       <c r="I27" t="n">
-        <v>189.9476123064429</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -29459,13 +29459,13 @@
         <v>319</v>
       </c>
       <c r="S27" t="n">
-        <v>96.05772723972444</v>
+        <v>319</v>
       </c>
       <c r="T27" t="n">
-        <v>319</v>
+        <v>286.0053395461671</v>
       </c>
       <c r="U27" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
         <v>319</v>
@@ -29474,7 +29474,7 @@
         <v>319</v>
       </c>
       <c r="X27" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
         <v>319</v>
@@ -29645,16 +29645,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>96.0577272397245</v>
+        <v>319</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="F30" t="n">
         <v>319</v>
@@ -29702,16 +29702,16 @@
         <v>319</v>
       </c>
       <c r="U30" t="n">
-        <v>319</v>
+        <v>96.05772723972433</v>
       </c>
       <c r="V30" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
         <v>319</v>
@@ -29851,7 +29851,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>158.200955612214</v>
+        <v>158.2009556122881</v>
       </c>
       <c r="S32" t="n">
         <v>319</v>
@@ -29882,10 +29882,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>319</v>
+        <v>168.3712564811474</v>
       </c>
       <c r="C33" t="n">
-        <v>96.05772723972427</v>
+        <v>319</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -29927,7 +29927,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>72.31352924142297</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>319</v>
@@ -30119,13 +30119,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>10.55655664627741</v>
+        <v>10.55655664629924</v>
       </c>
       <c r="C36" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>230.743341982337</v>
       </c>
       <c r="E36" t="n">
         <v>342.6720972219126</v>
@@ -30164,7 +30164,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>72.31352924142297</v>
       </c>
       <c r="R36" t="n">
         <v>397</v>
@@ -30179,16 +30179,16 @@
         <v>397</v>
       </c>
       <c r="V36" t="n">
-        <v>397</v>
+        <v>40.51066719149284</v>
       </c>
       <c r="W36" t="n">
         <v>397</v>
       </c>
       <c r="X36" t="n">
-        <v>354.0762332035993</v>
+        <v>397</v>
       </c>
       <c r="Y36" t="n">
-        <v>25.3913927660852</v>
+        <v>397</v>
       </c>
     </row>
     <row r="37">
@@ -30201,13 +30201,13 @@
         <v>287.1138003370787</v>
       </c>
       <c r="C37" t="n">
+        <v>272.7252466480447</v>
+      </c>
+      <c r="D37" t="n">
+        <v>285.5362180555555</v>
+      </c>
+      <c r="E37" t="n">
         <v>397</v>
-      </c>
-      <c r="D37" t="n">
-        <v>397</v>
-      </c>
-      <c r="E37" t="n">
-        <v>280.9809048369565</v>
       </c>
       <c r="F37" t="n">
         <v>274.3828559677419</v>
@@ -30219,16 +30219,16 @@
         <v>397</v>
       </c>
       <c r="I37" t="n">
+        <v>156.7312261119215</v>
+      </c>
+      <c r="J37" t="n">
+        <v>362.4794570326564</v>
+      </c>
+      <c r="K37" t="n">
         <v>397</v>
       </c>
-      <c r="J37" t="n">
-        <v>362.4794570326782</v>
-      </c>
-      <c r="K37" t="n">
-        <v>211.6312656044217</v>
-      </c>
       <c r="L37" t="n">
-        <v>348.252795779881</v>
+        <v>325.1555297971234</v>
       </c>
       <c r="M37" t="n">
         <v>397</v>
@@ -30252,7 +30252,7 @@
         <v>350.8400534733473</v>
       </c>
       <c r="T37" t="n">
-        <v>207.1968615882249</v>
+        <v>397</v>
       </c>
       <c r="U37" t="n">
         <v>150.9222929138022</v>
@@ -30261,7 +30261,7 @@
         <v>199.1703102162162</v>
       </c>
       <c r="W37" t="n">
-        <v>226.3728098387097</v>
+        <v>234.286417035571</v>
       </c>
       <c r="X37" t="n">
         <v>247.4436454301076</v>
@@ -30362,13 +30362,13 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G39" t="n">
         <v>324.9501396486123</v>
@@ -30401,7 +30401,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>72.31352924142297</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>397</v>
@@ -30416,16 +30416,16 @@
         <v>397</v>
       </c>
       <c r="V39" t="n">
-        <v>397</v>
+        <v>40.5106671914601</v>
       </c>
       <c r="W39" t="n">
-        <v>397</v>
+        <v>58.37314290976846</v>
       </c>
       <c r="X39" t="n">
-        <v>218.4624362880019</v>
+        <v>45.86273944532749</v>
       </c>
       <c r="Y39" t="n">
-        <v>397</v>
+        <v>306.7833895254474</v>
       </c>
     </row>
     <row r="40">
@@ -30444,16 +30444,16 @@
         <v>397</v>
       </c>
       <c r="E40" t="n">
-        <v>280.9809048369565</v>
+        <v>397</v>
       </c>
       <c r="F40" t="n">
-        <v>274.3828559677419</v>
+        <v>397</v>
       </c>
       <c r="G40" t="n">
-        <v>244.3820695628415</v>
+        <v>397</v>
       </c>
       <c r="H40" t="n">
-        <v>222.8870933147334</v>
+        <v>397</v>
       </c>
       <c r="I40" t="n">
         <v>156.7312261119215</v>
@@ -30489,22 +30489,22 @@
         <v>350.8400534733473</v>
       </c>
       <c r="T40" t="n">
-        <v>221.4731665461664</v>
+        <v>207.1968615882249</v>
       </c>
       <c r="U40" t="n">
-        <v>397</v>
+        <v>150.9222929138022</v>
       </c>
       <c r="V40" t="n">
-        <v>199.1703102162162</v>
+        <v>323.8754378243493</v>
       </c>
       <c r="W40" t="n">
-        <v>397</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X40" t="n">
-        <v>397</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y40" t="n">
-        <v>397</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="41">
@@ -30614,7 +30614,7 @@
         <v>293</v>
       </c>
       <c r="I42" t="n">
-        <v>187.5608388609467</v>
+        <v>189.9476123064429</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -30641,7 +30641,7 @@
         <v>72.31352924142297</v>
       </c>
       <c r="R42" t="n">
-        <v>293</v>
+        <v>290.6132265545748</v>
       </c>
       <c r="S42" t="n">
         <v>293</v>
@@ -30851,7 +30851,7 @@
         <v>293</v>
       </c>
       <c r="I45" t="n">
-        <v>189.9476123064429</v>
+        <v>187.5608388610177</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -30875,7 +30875,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>69.92675579599873</v>
+        <v>72.31352924142297</v>
       </c>
       <c r="R45" t="n">
         <v>293</v>
@@ -31820,10 +31820,10 @@
         <v>232.8255376884422</v>
       </c>
       <c r="M11" t="n">
-        <v>259.0632713567839</v>
+        <v>259.063271356784</v>
       </c>
       <c r="N11" t="n">
-        <v>263.2551859296482</v>
+        <v>263.2551859296483</v>
       </c>
       <c r="O11" t="n">
         <v>248.5844070351759</v>
@@ -32057,10 +32057,10 @@
         <v>232.8255376884422</v>
       </c>
       <c r="M14" t="n">
-        <v>259.0632713567839</v>
+        <v>259.063271356784</v>
       </c>
       <c r="N14" t="n">
-        <v>263.2551859296482</v>
+        <v>263.2551859296483</v>
       </c>
       <c r="O14" t="n">
         <v>248.5844070351759</v>
@@ -32294,10 +32294,10 @@
         <v>232.8255376884422</v>
       </c>
       <c r="M17" t="n">
-        <v>259.0632713567839</v>
+        <v>259.063271356784</v>
       </c>
       <c r="N17" t="n">
-        <v>263.2551859296482</v>
+        <v>263.2551859296483</v>
       </c>
       <c r="O17" t="n">
         <v>248.5844070351759</v>
@@ -32531,10 +32531,10 @@
         <v>232.8255376884422</v>
       </c>
       <c r="M20" t="n">
-        <v>259.0632713567839</v>
+        <v>259.063271356784</v>
       </c>
       <c r="N20" t="n">
-        <v>263.2551859296482</v>
+        <v>263.2551859296483</v>
       </c>
       <c r="O20" t="n">
         <v>248.5844070351759</v>
@@ -32768,10 +32768,10 @@
         <v>232.8255376884422</v>
       </c>
       <c r="M23" t="n">
-        <v>259.0632713567839</v>
+        <v>259.0632713567844</v>
       </c>
       <c r="N23" t="n">
-        <v>263.2551859296482</v>
+        <v>263.2551859296487</v>
       </c>
       <c r="O23" t="n">
         <v>248.5844070351759</v>
@@ -33005,10 +33005,10 @@
         <v>232.8255376884422</v>
       </c>
       <c r="M26" t="n">
-        <v>259.0632713567839</v>
+        <v>259.0632713567853</v>
       </c>
       <c r="N26" t="n">
-        <v>263.2551859296482</v>
+        <v>263.2551859296497</v>
       </c>
       <c r="O26" t="n">
         <v>248.5844070351759</v>
@@ -33242,10 +33242,10 @@
         <v>232.8255376884422</v>
       </c>
       <c r="M29" t="n">
-        <v>259.0632713567839</v>
+        <v>259.0632713567867</v>
       </c>
       <c r="N29" t="n">
-        <v>263.2551859296482</v>
+        <v>263.255185929651</v>
       </c>
       <c r="O29" t="n">
         <v>248.5844070351759</v>
@@ -33479,10 +33479,10 @@
         <v>232.8255376884422</v>
       </c>
       <c r="M32" t="n">
-        <v>259.0632713567839</v>
+        <v>259.0632713567876</v>
       </c>
       <c r="N32" t="n">
-        <v>263.2551859296482</v>
+        <v>263.2551859296519</v>
       </c>
       <c r="O32" t="n">
         <v>248.5844070351759</v>
@@ -33716,10 +33716,10 @@
         <v>232.8255376884422</v>
       </c>
       <c r="M35" t="n">
-        <v>259.0632713567839</v>
+        <v>259.0632713567894</v>
       </c>
       <c r="N35" t="n">
-        <v>263.2551859296482</v>
+        <v>263.2551859296537</v>
       </c>
       <c r="O35" t="n">
         <v>248.5844070351759</v>
@@ -33953,10 +33953,10 @@
         <v>232.8255376884422</v>
       </c>
       <c r="M38" t="n">
-        <v>259.0632713567839</v>
+        <v>259.0632713567921</v>
       </c>
       <c r="N38" t="n">
-        <v>263.2551859296482</v>
+        <v>263.2551859296565</v>
       </c>
       <c r="O38" t="n">
         <v>248.5844070351759</v>
@@ -34190,10 +34190,10 @@
         <v>232.8255376884422</v>
       </c>
       <c r="M41" t="n">
-        <v>259.0632713567839</v>
+        <v>259.0632713567931</v>
       </c>
       <c r="N41" t="n">
-        <v>263.2551859296482</v>
+        <v>263.2551859296574</v>
       </c>
       <c r="O41" t="n">
         <v>248.5844070351759</v>
@@ -34427,10 +34427,10 @@
         <v>232.8255376884422</v>
       </c>
       <c r="M44" t="n">
-        <v>259.0632713567839</v>
+        <v>259.0632713568021</v>
       </c>
       <c r="N44" t="n">
-        <v>263.2551859296482</v>
+        <v>263.2551859296665</v>
       </c>
       <c r="O44" t="n">
         <v>248.5844070351759</v>
@@ -34743,28 +34743,28 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>52.15992964824119</v>
+        <v>52.1599296482412</v>
       </c>
       <c r="L2" t="n">
-        <v>64.70900502512563</v>
+        <v>64.70900502512562</v>
       </c>
       <c r="M2" t="n">
-        <v>374</v>
+        <v>183.3412755627362</v>
       </c>
       <c r="N2" t="n">
         <v>374</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="P2" t="n">
         <v>58.67867865278593</v>
       </c>
       <c r="Q2" t="n">
-        <v>183.3412755627363</v>
+        <v>374</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34877,13 +34877,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23.59686059216742</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E4" t="n">
         <v>119.0190951630435</v>
@@ -34895,7 +34895,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>172.8642181606765</v>
+        <v>120.4777525520407</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -34904,10 +34904,10 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>132.8490622644307</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>3.798404629106074</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -34928,7 +34928,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>40.83199570698065</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -34937,10 +34937,10 @@
         <v>249.0516415124273</v>
       </c>
       <c r="V4" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>152.5563545698924</v>
@@ -34983,7 +34983,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>235.5012052109774</v>
+        <v>374</v>
       </c>
       <c r="L5" t="n">
         <v>64.70900502512563</v>
@@ -34992,7 +34992,7 @@
         <v>374</v>
       </c>
       <c r="N5" t="n">
-        <v>374</v>
+        <v>235.5012052109774</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -35117,19 +35117,19 @@
         <v>112.8861996629213</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
         <v>119.0190951630435</v>
       </c>
       <c r="F7" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>155.1400615846995</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>172.8642181606765</v>
@@ -35138,7 +35138,7 @@
         <v>228.8979542159473</v>
       </c>
       <c r="J7" t="n">
-        <v>166.900342550082</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>132.8490622644307</v>
@@ -35165,13 +35165,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>40.83199570698063</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>190.7613351330866</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>126.8820366004648</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -35180,7 +35180,7 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -35217,19 +35217,19 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
         <v>374</v>
       </c>
-      <c r="K8" t="n">
-        <v>373.9999999999999</v>
-      </c>
       <c r="L8" t="n">
+        <v>64.70900502512563</v>
+      </c>
+      <c r="M8" t="n">
         <v>374</v>
       </c>
-      <c r="M8" t="n">
-        <v>300.210210236103</v>
-      </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -35238,7 +35238,7 @@
         <v>58.67867865278593</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>235.5012052109774</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35351,7 +35351,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C10" t="n">
         <v>127.2747533519553</v>
@@ -35363,10 +35363,10 @@
         <v>119.0190951630435</v>
       </c>
       <c r="F10" t="n">
-        <v>121.1716831956828</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>66.36388431249102</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -35405,16 +35405,16 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>190.7613351330866</v>
       </c>
       <c r="U10" t="n">
         <v>249.0516415124273</v>
       </c>
       <c r="V10" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>152.5563545698924</v>
@@ -35460,13 +35460,13 @@
         <v>187.6734723618091</v>
       </c>
       <c r="L11" t="n">
-        <v>232.8255376884422</v>
+        <v>655</v>
       </c>
       <c r="M11" t="n">
-        <v>607.3433266784076</v>
+        <v>655</v>
       </c>
       <c r="N11" t="n">
-        <v>655</v>
+        <v>185.1688643668502</v>
       </c>
       <c r="O11" t="n">
         <v>178.3365374610834</v>
@@ -35615,7 +35615,7 @@
         <v>330.5205429673709</v>
       </c>
       <c r="K13" t="n">
-        <v>107.3687343955782</v>
+        <v>107.3687343955783</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -35691,28 +35691,28 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>520.4824991852875</v>
+        <v>90.1777625991308</v>
       </c>
       <c r="K14" t="n">
+        <v>655</v>
+      </c>
+      <c r="L14" t="n">
         <v>654.9999999999999</v>
       </c>
-      <c r="L14" t="n">
-        <v>232.8255376884422</v>
-      </c>
       <c r="M14" t="n">
-        <v>192.6633045704905</v>
+        <v>655</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>178.3365374610834</v>
+        <v>178.3365374610835</v>
       </c>
       <c r="P14" t="n">
         <v>211.8739801603236</v>
       </c>
       <c r="Q14" t="n">
-        <v>602.3534944697265</v>
+        <v>148.1470733148155</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35852,7 +35852,7 @@
         <v>330.5205429673709</v>
       </c>
       <c r="K16" t="n">
-        <v>107.3687343955782</v>
+        <v>107.3687343955783</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -35928,22 +35928,22 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>520.4824991852875</v>
+        <v>90.1777625991308</v>
       </c>
       <c r="K17" t="n">
+        <v>187.673472361809</v>
+      </c>
+      <c r="L17" t="n">
         <v>654.9999999999999</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
+        <v>615.4736009530062</v>
+      </c>
+      <c r="N17" t="n">
         <v>655</v>
       </c>
-      <c r="M17" t="n">
-        <v>372.8423367286592</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
       <c r="O17" t="n">
-        <v>178.3365374610834</v>
+        <v>178.3365374610835</v>
       </c>
       <c r="P17" t="n">
         <v>211.8739801603236</v>
@@ -36062,7 +36062,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>31.88619966292139</v>
+        <v>31.88619966292134</v>
       </c>
       <c r="C19" t="n">
         <v>46.27475335195533</v>
@@ -36168,16 +36168,16 @@
         <v>520.4824991852875</v>
       </c>
       <c r="K20" t="n">
-        <v>655.0000000000184</v>
+        <v>654.9999999999999</v>
       </c>
       <c r="L20" t="n">
         <v>232.8255376884422</v>
       </c>
       <c r="M20" t="n">
-        <v>192.6633045705454</v>
+        <v>140.0167990402171</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>655.0000000000001</v>
       </c>
       <c r="O20" t="n">
         <v>178.3365374610834</v>
@@ -36186,7 +36186,7 @@
         <v>211.8739801603236</v>
       </c>
       <c r="Q20" t="n">
-        <v>602.3534944697265</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36326,7 +36326,7 @@
         <v>330.5205429673709</v>
       </c>
       <c r="K22" t="n">
-        <v>107.3687343955782</v>
+        <v>107.3687343955783</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -36405,16 +36405,16 @@
         <v>520.4824991852875</v>
       </c>
       <c r="K23" t="n">
-        <v>187.673472361809</v>
+        <v>654.9999999999999</v>
       </c>
       <c r="L23" t="n">
         <v>232.8255376884422</v>
       </c>
       <c r="M23" t="n">
-        <v>4.98983220874726</v>
+        <v>140.0167990402167</v>
       </c>
       <c r="N23" t="n">
-        <v>655.0000000000076</v>
+        <v>655.0000000000001</v>
       </c>
       <c r="O23" t="n">
         <v>178.3365374610834</v>
@@ -36423,7 +36423,7 @@
         <v>211.8739801603236</v>
       </c>
       <c r="Q23" t="n">
-        <v>602.3534944697265</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36563,7 +36563,7 @@
         <v>330.5205429673709</v>
       </c>
       <c r="K25" t="n">
-        <v>107.3687343955783</v>
+        <v>107.3687343955782</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -36639,31 +36639,31 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>520.4824991852875</v>
+        <v>90.1777625991308</v>
       </c>
       <c r="K26" t="n">
         <v>187.673472361809</v>
       </c>
       <c r="L26" t="n">
-        <v>232.8255376884422</v>
+        <v>232.8255376884423</v>
       </c>
       <c r="M26" t="n">
-        <v>4.989832208742897</v>
+        <v>655.0000000000019</v>
       </c>
       <c r="N26" t="n">
-        <v>655.000000000011</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>178.3365374610834</v>
       </c>
       <c r="P26" t="n">
-        <v>211.8739801603236</v>
+        <v>647.1685489551596</v>
       </c>
       <c r="Q26" t="n">
         <v>602.3534944697265</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.250769716508762e-11</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -36879,16 +36879,16 @@
         <v>90.1777625991308</v>
       </c>
       <c r="K29" t="n">
-        <v>655.0000000000183</v>
+        <v>187.673472361809</v>
       </c>
       <c r="L29" t="n">
-        <v>655.0000000000183</v>
+        <v>232.8255376884423</v>
       </c>
       <c r="M29" t="n">
-        <v>148.1470733148302</v>
+        <v>435.2945687948322</v>
       </c>
       <c r="N29" t="n">
-        <v>655.0000000000167</v>
+        <v>655.0000000000058</v>
       </c>
       <c r="O29" t="n">
         <v>178.3365374610834</v>
@@ -36897,7 +36897,7 @@
         <v>211.8739801603236</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>602.3534944697265</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -37037,7 +37037,7 @@
         <v>330.5205429673709</v>
       </c>
       <c r="K31" t="n">
-        <v>107.3687343955782</v>
+        <v>107.3687343955783</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -37119,25 +37119,25 @@
         <v>187.673472361809</v>
       </c>
       <c r="L32" t="n">
-        <v>232.8255376884422</v>
+        <v>654.9999999999999</v>
       </c>
       <c r="M32" t="n">
-        <v>560.9846007256691</v>
+        <v>655.000000000011</v>
       </c>
       <c r="N32" t="n">
-        <v>655.0000000000256</v>
+        <v>13.12010648326908</v>
       </c>
       <c r="O32" t="n">
-        <v>655.0000000000256</v>
+        <v>178.3365374610834</v>
       </c>
       <c r="P32" t="n">
         <v>211.8739801603236</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>602.3534944697265</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>7.395386211385931e-11</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -37353,16 +37353,16 @@
         <v>90.1777625991308</v>
       </c>
       <c r="K35" t="n">
-        <v>374.0000000000183</v>
+        <v>187.673472361809</v>
       </c>
       <c r="L35" t="n">
-        <v>232.8255376884422</v>
+        <v>232.8255376884423</v>
       </c>
       <c r="M35" t="n">
-        <v>19.67507097991389</v>
+        <v>206.0015986180723</v>
       </c>
       <c r="N35" t="n">
-        <v>374.0000000000492</v>
+        <v>374.0000000000273</v>
       </c>
       <c r="O35" t="n">
         <v>178.3365374610834</v>
@@ -37429,13 +37429,13 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>38.03935242797332</v>
+        <v>199.7892383131474</v>
       </c>
       <c r="K36" t="n">
         <v>22.69379302306083</v>
       </c>
       <c r="L36" t="n">
-        <v>374.0000000000492</v>
+        <v>374.0000000000273</v>
       </c>
       <c r="M36" t="n">
         <v>286.9650421645043</v>
@@ -37444,7 +37444,7 @@
         <v>339.9353519954473</v>
       </c>
       <c r="O36" t="n">
-        <v>374.0000000000492</v>
+        <v>212.2501141148244</v>
       </c>
       <c r="P36" t="n">
         <v>45.25534927787736</v>
@@ -37487,13 +37487,13 @@
         <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>124.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>111.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>116.0190951630435</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -37505,16 +37505,16 @@
         <v>174.1129066852666</v>
       </c>
       <c r="I37" t="n">
-        <v>240.2687738880785</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>374.0000000000492</v>
+        <v>374.0000000000273</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>185.3687343955783</v>
       </c>
       <c r="L37" t="n">
-        <v>23.09726598275758</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -37538,7 +37538,7 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>189.8031384117751</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -37547,7 +37547,7 @@
         <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>7.913607196861285</v>
       </c>
       <c r="X37" t="n">
         <v>0</v>
@@ -37590,16 +37590,16 @@
         <v>90.1777625991308</v>
       </c>
       <c r="K38" t="n">
-        <v>374.0000000000183</v>
+        <v>187.673472361809</v>
       </c>
       <c r="L38" t="n">
-        <v>232.8255376884422</v>
+        <v>232.8255376884423</v>
       </c>
       <c r="M38" t="n">
-        <v>19.67507097989391</v>
+        <v>206.0015986180395</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>374.0000000000601</v>
       </c>
       <c r="O38" t="n">
         <v>178.3365374610834</v>
@@ -37608,7 +37608,7 @@
         <v>211.8739801603236</v>
       </c>
       <c r="Q38" t="n">
-        <v>374.0000000000692</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37666,13 +37666,13 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>38.0393524279333</v>
+        <v>38.03935242787885</v>
       </c>
       <c r="K39" t="n">
         <v>22.69379302306083</v>
       </c>
       <c r="L39" t="n">
-        <v>374.0000000000692</v>
+        <v>374.0000000000601</v>
       </c>
       <c r="M39" t="n">
         <v>286.9650421645043</v>
@@ -37681,7 +37681,7 @@
         <v>339.9353519954473</v>
       </c>
       <c r="O39" t="n">
-        <v>374.0000000000692</v>
+        <v>374.0000000000601</v>
       </c>
       <c r="P39" t="n">
         <v>45.25534927787736</v>
@@ -37730,16 +37730,16 @@
         <v>111.4637819444445</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>116.0190951630435</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>122.6171440322581</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>152.6179304371585</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>174.1129066852666</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
@@ -37775,22 +37775,22 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>14.27630495794146</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>246.0777070861978</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>124.7051276081331</v>
       </c>
       <c r="W40" t="n">
-        <v>170.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>149.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>109.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -37830,16 +37830,16 @@
         <v>187.673472361809</v>
       </c>
       <c r="L41" t="n">
-        <v>232.8255376884422</v>
+        <v>232.8255376884423</v>
       </c>
       <c r="M41" t="n">
-        <v>374.0000000001165</v>
+        <v>10.33813607901569</v>
       </c>
       <c r="N41" t="n">
-        <v>206.0015986180558</v>
+        <v>374.0000000000837</v>
       </c>
       <c r="O41" t="n">
-        <v>178.3365374610834</v>
+        <v>374.0000000000837</v>
       </c>
       <c r="P41" t="n">
         <v>211.8739801603236</v>
@@ -37903,13 +37903,13 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>146.2959740893367</v>
+        <v>38.0393524278316</v>
       </c>
       <c r="K42" t="n">
         <v>22.69379302306083</v>
       </c>
       <c r="L42" t="n">
-        <v>374.0000000001165</v>
+        <v>374.0000000000837</v>
       </c>
       <c r="M42" t="n">
         <v>286.9650421645043</v>
@@ -37918,10 +37918,10 @@
         <v>339.9353519954473</v>
       </c>
       <c r="O42" t="n">
-        <v>46.59266649806909</v>
+        <v>374.0000000000837</v>
       </c>
       <c r="P42" t="n">
-        <v>264.4060611184268</v>
+        <v>45.25534927787736</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -37979,13 +37979,13 @@
         <v>70.11290668526664</v>
       </c>
       <c r="I43" t="n">
-        <v>136.2687738880784</v>
+        <v>136.2687738880785</v>
       </c>
       <c r="J43" t="n">
         <v>304.5205429673709</v>
       </c>
       <c r="K43" t="n">
-        <v>81.36873439557824</v>
+        <v>81.36873439557826</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -38012,7 +38012,7 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>85.80313841177507</v>
+        <v>85.80313841177508</v>
       </c>
       <c r="U43" t="n">
         <v>142.0777070861978</v>
@@ -38061,19 +38061,19 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>374.0000000001892</v>
+        <v>90.1777625991308</v>
       </c>
       <c r="K44" t="n">
-        <v>187.6734723618091</v>
+        <v>187.673472361809</v>
       </c>
       <c r="L44" t="n">
-        <v>232.8255376884422</v>
+        <v>232.8255376884423</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>374.000000000182</v>
       </c>
       <c r="N44" t="n">
-        <v>296.1793612170405</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>178.3365374610834</v>
@@ -38082,7 +38082,7 @@
         <v>211.8739801603236</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>206.0015986179178</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38140,13 +38140,13 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>69.56644506672652</v>
+        <v>135.487214905926</v>
       </c>
       <c r="K45" t="n">
-        <v>318.5740338860743</v>
+        <v>22.69379302306083</v>
       </c>
       <c r="L45" t="n">
-        <v>374.0000000001892</v>
+        <v>57.40142568134173</v>
       </c>
       <c r="M45" t="n">
         <v>286.9650421645043</v>
@@ -38155,10 +38155,10 @@
         <v>339.9353519954473</v>
       </c>
       <c r="O45" t="n">
-        <v>46.59266649806909</v>
+        <v>374.000000000182</v>
       </c>
       <c r="P45" t="n">
-        <v>45.25534927787736</v>
+        <v>264.4060611184268</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -38216,13 +38216,13 @@
         <v>70.11290668526664</v>
       </c>
       <c r="I46" t="n">
-        <v>136.2687738880785</v>
+        <v>136.2687738880784</v>
       </c>
       <c r="J46" t="n">
         <v>304.5205429673709</v>
       </c>
       <c r="K46" t="n">
-        <v>81.36873439557826</v>
+        <v>81.36873439557824</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -38249,7 +38249,7 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>85.80313841177508</v>
+        <v>85.80313841177507</v>
       </c>
       <c r="U46" t="n">
         <v>142.0777070861978</v>
